--- a/research/traditional_assets/database/data/luxembourg/luxembourg_broadcasting.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_broadcasting.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07525562698990837</v>
+        <v>0.07510171645619554</v>
       </c>
       <c r="C2">
-        <v>5851.4078387102</v>
+        <v>5801.976062739674</v>
       </c>
       <c r="D2">
-        <v>5360.7078387102</v>
+        <v>5374.012062739675</v>
       </c>
       <c r="E2">
-        <v>-1996.1</v>
+        <v>-1933.364</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>62.736</v>
       </c>
       <c r="G2">
         <v>490.7</v>
@@ -1457,28 +1457,28 @@
         <v>571.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.1556208</v>
       </c>
       <c r="N2">
-        <v>571.1</v>
+        <v>567.9443792000001</v>
       </c>
       <c r="O2">
-        <v>142.43234</v>
+        <v>141.64532817248</v>
       </c>
       <c r="P2">
-        <v>428.66766</v>
+        <v>426.29905102752</v>
       </c>
       <c r="Q2">
-        <v>684.76766</v>
+        <v>682.39905102752</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07525562698990837</v>
+        <v>0.07547895419817731</v>
       </c>
       <c r="T2">
-        <v>0.6802685217068908</v>
+        <v>0.6854261939532866</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>180.9786524413834</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07510171645619554</v>
+        <v>0.07494780592248271</v>
       </c>
       <c r="C3">
-        <v>5801.976062739674</v>
+        <v>5752.610488009894</v>
       </c>
       <c r="D3">
-        <v>5374.012062739675</v>
+        <v>5387.382488009894</v>
       </c>
       <c r="E3">
-        <v>-1933.364</v>
+        <v>-1870.628</v>
       </c>
       <c r="F3">
-        <v>62.736</v>
+        <v>125.472</v>
       </c>
       <c r="G3">
         <v>490.7</v>
@@ -1539,28 +1539,28 @@
         <v>571.1</v>
       </c>
       <c r="M3">
-        <v>3.1556208</v>
+        <v>6.3112416</v>
       </c>
       <c r="N3">
-        <v>567.9443792000001</v>
+        <v>564.7887584</v>
       </c>
       <c r="O3">
-        <v>141.64532817248</v>
+        <v>140.85831634496</v>
       </c>
       <c r="P3">
-        <v>426.29905102752</v>
+        <v>423.93044205504</v>
       </c>
       <c r="Q3">
-        <v>682.39905102752</v>
+        <v>680.03044205504</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07547895419817731</v>
+        <v>0.07570683910457419</v>
       </c>
       <c r="T3">
-        <v>0.6854261939532866</v>
+        <v>0.690689124816956</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>180.9786524413834</v>
+        <v>90.48932622069167</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07494780592248271</v>
+        <v>0.07479389538876988</v>
       </c>
       <c r="C4">
-        <v>5752.610488009894</v>
+        <v>5703.311609875034</v>
       </c>
       <c r="D4">
-        <v>5387.382488009894</v>
+        <v>5400.819609875034</v>
       </c>
       <c r="E4">
-        <v>-1870.628</v>
+        <v>-1807.892</v>
       </c>
       <c r="F4">
-        <v>125.472</v>
+        <v>188.208</v>
       </c>
       <c r="G4">
         <v>490.7</v>
@@ -1621,28 +1621,28 @@
         <v>571.1</v>
       </c>
       <c r="M4">
-        <v>6.3112416</v>
+        <v>9.4668624</v>
       </c>
       <c r="N4">
-        <v>564.7887584</v>
+        <v>561.6331376000001</v>
       </c>
       <c r="O4">
-        <v>140.85831634496</v>
+        <v>140.07130451744</v>
       </c>
       <c r="P4">
-        <v>423.93044205504</v>
+        <v>421.56183308256</v>
       </c>
       <c r="Q4">
-        <v>680.03044205504</v>
+        <v>677.6618330825601</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07570683910457419</v>
+        <v>0.07593942266883492</v>
       </c>
       <c r="T4">
-        <v>0.690689124816956</v>
+        <v>0.6960605697190513</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>90.48932622069167</v>
+        <v>60.32621748046111</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07479389538876988</v>
+        <v>0.07463998485505705</v>
       </c>
       <c r="C5">
-        <v>5703.311609875034</v>
+        <v>5654.079928643646</v>
       </c>
       <c r="D5">
-        <v>5400.819609875034</v>
+        <v>5414.323928643646</v>
       </c>
       <c r="E5">
-        <v>-1807.892</v>
+        <v>-1745.156</v>
       </c>
       <c r="F5">
-        <v>188.208</v>
+        <v>250.944</v>
       </c>
       <c r="G5">
         <v>490.7</v>
@@ -1703,28 +1703,28 @@
         <v>571.1</v>
       </c>
       <c r="M5">
-        <v>9.4668624</v>
+        <v>12.6224832</v>
       </c>
       <c r="N5">
-        <v>561.6331376000001</v>
+        <v>558.4775168</v>
       </c>
       <c r="O5">
-        <v>140.07130451744</v>
+        <v>139.28429268992</v>
       </c>
       <c r="P5">
-        <v>421.56183308256</v>
+        <v>419.19322411008</v>
       </c>
       <c r="Q5">
-        <v>677.6618330825601</v>
+        <v>675.29322411008</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07593942266883492</v>
+        <v>0.07617685172401775</v>
       </c>
       <c r="T5">
-        <v>0.6960605697190513</v>
+        <v>0.7015439197232738</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>60.32621748046111</v>
+        <v>45.24466311034583</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07463998485505705</v>
+        <v>0.07448607432134421</v>
       </c>
       <c r="C6">
-        <v>5654.079928643646</v>
+        <v>5604.915949640754</v>
       </c>
       <c r="D6">
-        <v>5414.323928643646</v>
+        <v>5427.895949640754</v>
       </c>
       <c r="E6">
-        <v>-1745.156</v>
+        <v>-1682.42</v>
       </c>
       <c r="F6">
-        <v>250.944</v>
+        <v>313.6800000000001</v>
       </c>
       <c r="G6">
         <v>490.7</v>
@@ -1785,28 +1785,28 @@
         <v>571.1</v>
       </c>
       <c r="M6">
-        <v>12.6224832</v>
+        <v>15.778104</v>
       </c>
       <c r="N6">
-        <v>558.4775168</v>
+        <v>555.321896</v>
       </c>
       <c r="O6">
-        <v>139.28429268992</v>
+        <v>138.4972808624</v>
       </c>
       <c r="P6">
-        <v>419.19322411008</v>
+        <v>416.8246151376001</v>
       </c>
       <c r="Q6">
-        <v>675.29322411008</v>
+        <v>672.9246151376001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07617685172401775</v>
+        <v>0.07641927928562549</v>
       </c>
       <c r="T6">
-        <v>0.7015439197232738</v>
+        <v>0.7071427086749535</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>45.24466311034583</v>
+        <v>36.19573048827666</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07448607432134421</v>
+        <v>0.07433216378763138</v>
       </c>
       <c r="C7">
-        <v>5604.915949640754</v>
+        <v>5555.820183270878</v>
       </c>
       <c r="D7">
-        <v>5427.895949640754</v>
+        <v>5441.536183270879</v>
       </c>
       <c r="E7">
-        <v>-1682.42</v>
+        <v>-1619.684</v>
       </c>
       <c r="F7">
-        <v>313.6800000000001</v>
+        <v>376.4160000000001</v>
       </c>
       <c r="G7">
         <v>490.7</v>
@@ -1867,28 +1867,28 @@
         <v>571.1</v>
       </c>
       <c r="M7">
-        <v>15.778104</v>
+        <v>18.9337248</v>
       </c>
       <c r="N7">
-        <v>555.321896</v>
+        <v>552.1662752</v>
       </c>
       <c r="O7">
-        <v>138.4972808624</v>
+        <v>137.71026903488</v>
       </c>
       <c r="P7">
-        <v>416.8246151376001</v>
+        <v>414.45600616512</v>
       </c>
       <c r="Q7">
-        <v>672.9246151376001</v>
+        <v>670.55600616512</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07641927928562549</v>
+        <v>0.07666686488045892</v>
       </c>
       <c r="T7">
-        <v>0.7071427086749535</v>
+        <v>0.7128606207958179</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.19573048827666</v>
+        <v>30.16310874023055</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07433216378763138</v>
+        <v>0.07417825325391855</v>
       </c>
       <c r="C8">
-        <v>5555.820183270878</v>
+        <v>5506.793145082028</v>
       </c>
       <c r="D8">
-        <v>5441.536183270879</v>
+        <v>5455.245145082028</v>
       </c>
       <c r="E8">
-        <v>-1619.684</v>
+        <v>-1556.948</v>
       </c>
       <c r="F8">
-        <v>376.416</v>
+        <v>439.152</v>
       </c>
       <c r="G8">
         <v>490.7</v>
@@ -1949,28 +1949,28 @@
         <v>571.1</v>
       </c>
       <c r="M8">
-        <v>18.9337248</v>
+        <v>22.0893456</v>
       </c>
       <c r="N8">
-        <v>552.1662752</v>
+        <v>549.0106544</v>
       </c>
       <c r="O8">
-        <v>137.71026903488</v>
+        <v>136.92325720736</v>
       </c>
       <c r="P8">
-        <v>414.45600616512</v>
+        <v>412.08739719264</v>
       </c>
       <c r="Q8">
-        <v>670.55600616512</v>
+        <v>668.18739719264</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07666686488045892</v>
+        <v>0.07691977489668661</v>
       </c>
       <c r="T8">
-        <v>0.7128606207958179</v>
+        <v>0.718701498768744</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.16310874023055</v>
+        <v>25.85409320591191</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07417825325391855</v>
+        <v>0.07402434272020572</v>
       </c>
       <c r="C9">
-        <v>5506.793145082028</v>
+        <v>5457.835355830653</v>
       </c>
       <c r="D9">
-        <v>5455.245145082028</v>
+        <v>5469.023355830653</v>
       </c>
       <c r="E9">
-        <v>-1556.948</v>
+        <v>-1494.212</v>
       </c>
       <c r="F9">
-        <v>439.152</v>
+        <v>501.888</v>
       </c>
       <c r="G9">
         <v>490.7</v>
@@ -2031,28 +2031,28 @@
         <v>571.1</v>
       </c>
       <c r="M9">
-        <v>22.0893456</v>
+        <v>25.2449664</v>
       </c>
       <c r="N9">
-        <v>549.0106544</v>
+        <v>545.8550336000001</v>
       </c>
       <c r="O9">
-        <v>136.92325720736</v>
+        <v>136.13624537984</v>
       </c>
       <c r="P9">
-        <v>412.08739719264</v>
+        <v>409.71878822016</v>
       </c>
       <c r="Q9">
-        <v>668.18739719264</v>
+        <v>665.8187882201601</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07691977489668661</v>
+        <v>0.07717818295674535</v>
       </c>
       <c r="T9">
-        <v>0.718701498768744</v>
+        <v>0.7246693523497771</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.8540932059119</v>
+        <v>22.62233155517292</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07402434272020572</v>
+        <v>0.0738704321864929</v>
       </c>
       <c r="C10">
-        <v>5457.835355830653</v>
+        <v>5408.947341547579</v>
       </c>
       <c r="D10">
-        <v>5469.023355830653</v>
+        <v>5482.871341547579</v>
       </c>
       <c r="E10">
-        <v>-1494.212</v>
+        <v>-1431.476</v>
       </c>
       <c r="F10">
-        <v>501.888</v>
+        <v>564.624</v>
       </c>
       <c r="G10">
         <v>490.7</v>
@@ -2113,28 +2113,28 @@
         <v>571.1</v>
       </c>
       <c r="M10">
-        <v>25.2449664</v>
+        <v>28.4005872</v>
       </c>
       <c r="N10">
-        <v>545.8550336000001</v>
+        <v>542.6994128</v>
       </c>
       <c r="O10">
-        <v>136.13624537984</v>
+        <v>135.34923355232</v>
       </c>
       <c r="P10">
-        <v>409.71878822016</v>
+        <v>407.35017924768</v>
       </c>
       <c r="Q10">
-        <v>665.8187882201601</v>
+        <v>663.45017924768</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07717818295674535</v>
+        <v>0.07744227031482735</v>
       </c>
       <c r="T10">
-        <v>0.7246693523497771</v>
+        <v>0.7307683675479758</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.62233155517292</v>
+        <v>20.1087391601537</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0738704321864929</v>
+        <v>0.07371652165278006</v>
       </c>
       <c r="C11">
-        <v>5408.947341547579</v>
+        <v>5360.129633604965</v>
       </c>
       <c r="D11">
-        <v>5482.871341547579</v>
+        <v>5496.789633604965</v>
       </c>
       <c r="E11">
-        <v>-1431.476</v>
+        <v>-1368.74</v>
       </c>
       <c r="F11">
-        <v>564.624</v>
+        <v>627.36</v>
       </c>
       <c r="G11">
         <v>490.7</v>
@@ -2195,28 +2195,28 @@
         <v>571.1</v>
       </c>
       <c r="M11">
-        <v>28.4005872</v>
+        <v>31.556208</v>
       </c>
       <c r="N11">
-        <v>542.6994128</v>
+        <v>539.5437920000001</v>
       </c>
       <c r="O11">
-        <v>135.34923355232</v>
+        <v>134.5622217248</v>
       </c>
       <c r="P11">
-        <v>407.35017924768</v>
+        <v>404.9815702752001</v>
       </c>
       <c r="Q11">
-        <v>663.45017924768</v>
+        <v>661.0815702752001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07744227031482735</v>
+        <v>0.07771222628086673</v>
       </c>
       <c r="T11">
-        <v>0.7307683675479758</v>
+        <v>0.7370029164172455</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.1087391601537</v>
+        <v>18.09786524413834</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07371652165278006</v>
+        <v>0.07356261111906723</v>
       </c>
       <c r="C12">
-        <v>5360.129633604965</v>
+        <v>5311.382768784259</v>
       </c>
       <c r="D12">
-        <v>5496.789633604965</v>
+        <v>5510.778768784258</v>
       </c>
       <c r="E12">
-        <v>-1368.74</v>
+        <v>-1306.004</v>
       </c>
       <c r="F12">
-        <v>627.3600000000001</v>
+        <v>690.096</v>
       </c>
       <c r="G12">
         <v>490.7</v>
@@ -2277,28 +2277,28 @@
         <v>571.1</v>
       </c>
       <c r="M12">
-        <v>31.55620800000001</v>
+        <v>34.7118288</v>
       </c>
       <c r="N12">
-        <v>539.5437920000001</v>
+        <v>536.3881712</v>
       </c>
       <c r="O12">
-        <v>134.5622217248</v>
+        <v>133.77520989728</v>
       </c>
       <c r="P12">
-        <v>404.9815702752001</v>
+        <v>402.61296130272</v>
       </c>
       <c r="Q12">
-        <v>661.0815702752001</v>
+        <v>658.71296130272</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07771222628086673</v>
+        <v>0.07798824867310925</v>
       </c>
       <c r="T12">
-        <v>0.7370029164172455</v>
+        <v>0.7433775675082965</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.09786524413833</v>
+        <v>16.45260476739848</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07356261111906723</v>
+        <v>0.07340870058535438</v>
       </c>
       <c r="C13">
-        <v>5311.382768784259</v>
+        <v>5262.707289345209</v>
       </c>
       <c r="D13">
-        <v>5510.778768784258</v>
+        <v>5524.839289345209</v>
       </c>
       <c r="E13">
-        <v>-1306.004</v>
+        <v>-1243.268</v>
       </c>
       <c r="F13">
-        <v>690.096</v>
+        <v>752.832</v>
       </c>
       <c r="G13">
         <v>490.7</v>
@@ -2359,28 +2359,28 @@
         <v>571.1</v>
       </c>
       <c r="M13">
-        <v>34.7118288</v>
+        <v>37.8674496</v>
       </c>
       <c r="N13">
-        <v>536.3881712</v>
+        <v>533.2325504</v>
       </c>
       <c r="O13">
-        <v>133.77520989728</v>
+        <v>132.98819806976</v>
       </c>
       <c r="P13">
-        <v>402.61296130272</v>
+        <v>400.24435233024</v>
       </c>
       <c r="Q13">
-        <v>658.71296130272</v>
+        <v>656.3443523302401</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07798824867310925</v>
+        <v>0.07827054430153908</v>
       </c>
       <c r="T13">
-        <v>0.7433775675082965</v>
+        <v>0.7498970970332351</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.45260476739848</v>
+        <v>15.08155437011528</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07340870058535438</v>
+        <v>0.07325479005164155</v>
       </c>
       <c r="C14">
-        <v>5262.707289345209</v>
+        <v>5214.103743095934</v>
       </c>
       <c r="D14">
-        <v>5524.839289345209</v>
+        <v>5538.971743095934</v>
       </c>
       <c r="E14">
-        <v>-1243.268</v>
+        <v>-1180.532</v>
       </c>
       <c r="F14">
-        <v>752.832</v>
+        <v>815.5680000000001</v>
       </c>
       <c r="G14">
         <v>490.7</v>
@@ -2441,28 +2441,28 @@
         <v>571.1</v>
       </c>
       <c r="M14">
-        <v>37.8674496</v>
+        <v>41.0230704</v>
       </c>
       <c r="N14">
-        <v>533.2325504</v>
+        <v>530.0769296</v>
       </c>
       <c r="O14">
-        <v>132.98819806976</v>
+        <v>132.20118624224</v>
       </c>
       <c r="P14">
-        <v>400.24435233024</v>
+        <v>397.87574335776</v>
       </c>
       <c r="Q14">
-        <v>656.3443523302401</v>
+        <v>653.9757433577599</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07827054430153908</v>
+        <v>0.07855932948464547</v>
       </c>
       <c r="T14">
-        <v>0.7498970970332351</v>
+        <v>0.7565665008001264</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.08155437011528</v>
+        <v>13.92143480318333</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07325479005164155</v>
+        <v>0.07310087951792872</v>
       </c>
       <c r="C15">
-        <v>5214.103743095934</v>
+        <v>5165.572683464066</v>
       </c>
       <c r="D15">
-        <v>5538.971743095934</v>
+        <v>5553.176683464067</v>
       </c>
       <c r="E15">
-        <v>-1180.532</v>
+        <v>-1117.796</v>
       </c>
       <c r="F15">
-        <v>815.5680000000001</v>
+        <v>878.3040000000001</v>
       </c>
       <c r="G15">
         <v>490.7</v>
@@ -2523,28 +2523,28 @@
         <v>571.1</v>
       </c>
       <c r="M15">
-        <v>41.0230704</v>
+        <v>44.1786912</v>
       </c>
       <c r="N15">
-        <v>530.0769296</v>
+        <v>526.9213088</v>
       </c>
       <c r="O15">
-        <v>132.20118624224</v>
+        <v>131.41417441472</v>
       </c>
       <c r="P15">
-        <v>397.87574335776</v>
+        <v>395.50713438528</v>
       </c>
       <c r="Q15">
-        <v>653.9757433577599</v>
+        <v>651.60713438528</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07855932948464547</v>
+        <v>0.07885483060224271</v>
       </c>
       <c r="T15">
-        <v>0.7565665008001264</v>
+        <v>0.7633910069802012</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>13.92143480318333</v>
+        <v>12.92704660295595</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07310087951792872</v>
+        <v>0.07311585398421588</v>
       </c>
       <c r="C16">
-        <v>5165.572683464066</v>
+        <v>5101.451439021816</v>
       </c>
       <c r="D16">
-        <v>5553.176683464067</v>
+        <v>5551.791439021816</v>
       </c>
       <c r="E16">
-        <v>-1117.796</v>
+        <v>-1055.06</v>
       </c>
       <c r="F16">
-        <v>878.3040000000001</v>
+        <v>941.0400000000002</v>
       </c>
       <c r="G16">
         <v>490.7</v>
@@ -2605,45 +2605,45 @@
         <v>571.1</v>
       </c>
       <c r="M16">
-        <v>44.1786912</v>
+        <v>48.74587200000001</v>
       </c>
       <c r="N16">
-        <v>526.9213088</v>
+        <v>522.3541280000001</v>
       </c>
       <c r="O16">
-        <v>131.41417441472</v>
+        <v>130.2751195232</v>
       </c>
       <c r="P16">
-        <v>395.50713438528</v>
+        <v>392.0790084768</v>
       </c>
       <c r="Q16">
-        <v>651.60713438528</v>
+        <v>648.1790084768</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07885483060224271</v>
+        <v>0.07915728468731281</v>
       </c>
       <c r="T16">
-        <v>0.7633910069802012</v>
+        <v>0.7703760897762776</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.2494</v>
       </c>
       <c r="W16">
-        <v>0.03775517999999999</v>
+        <v>0.03888108</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>12.92704660295595</v>
+        <v>11.71586385817449</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07311585398421588</v>
+        <v>0.07297320245050307</v>
       </c>
       <c r="C17">
-        <v>5101.451439021816</v>
+        <v>5051.93985262421</v>
       </c>
       <c r="D17">
-        <v>5551.791439021816</v>
+        <v>5565.01585262421</v>
       </c>
       <c r="E17">
-        <v>-1055.06</v>
+        <v>-992.3240000000001</v>
       </c>
       <c r="F17">
-        <v>941.04</v>
+        <v>1003.776</v>
       </c>
       <c r="G17">
         <v>490.7</v>
@@ -2687,28 +2687,28 @@
         <v>571.1</v>
       </c>
       <c r="M17">
-        <v>48.745872</v>
+        <v>51.9955968</v>
       </c>
       <c r="N17">
-        <v>522.3541280000001</v>
+        <v>519.1044032</v>
       </c>
       <c r="O17">
-        <v>130.2751195232</v>
+        <v>129.46463815808</v>
       </c>
       <c r="P17">
-        <v>392.0790084768</v>
+        <v>389.63976504192</v>
       </c>
       <c r="Q17">
-        <v>648.1790084768</v>
+        <v>645.73976504192</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07915728468731281</v>
+        <v>0.0794669400601227</v>
       </c>
       <c r="T17">
-        <v>0.7703760897762776</v>
+        <v>0.7775274840674988</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.7158638581745</v>
+        <v>10.98362236703859</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07297320245050307</v>
+        <v>0.07283055091679023</v>
       </c>
       <c r="C18">
-        <v>5051.93985262421</v>
+        <v>5002.491417982041</v>
       </c>
       <c r="D18">
-        <v>5565.01585262421</v>
+        <v>5578.303417982042</v>
       </c>
       <c r="E18">
-        <v>-992.3240000000001</v>
+        <v>-929.588</v>
       </c>
       <c r="F18">
-        <v>1003.776</v>
+        <v>1066.512</v>
       </c>
       <c r="G18">
         <v>490.7</v>
@@ -2769,28 +2769,28 @@
         <v>571.1</v>
       </c>
       <c r="M18">
-        <v>51.9955968</v>
+        <v>55.24532160000001</v>
       </c>
       <c r="N18">
-        <v>519.1044032</v>
+        <v>515.8546784</v>
       </c>
       <c r="O18">
-        <v>129.46463815808</v>
+        <v>128.65415679296</v>
       </c>
       <c r="P18">
-        <v>389.63976504192</v>
+        <v>387.20052160704</v>
       </c>
       <c r="Q18">
-        <v>645.73976504192</v>
+        <v>643.3005216070401</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0794669400601227</v>
+        <v>0.079784057008181</v>
       </c>
       <c r="T18">
-        <v>0.7775274840674988</v>
+        <v>0.7848512011127253</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.98362236703859</v>
+        <v>10.33752693368337</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07283055091679023</v>
+        <v>0.07291758298307741</v>
       </c>
       <c r="C19">
-        <v>5002.491417982041</v>
+        <v>4931.641104226298</v>
       </c>
       <c r="D19">
-        <v>5578.303417982042</v>
+        <v>5570.189104226299</v>
       </c>
       <c r="E19">
-        <v>-929.588</v>
+        <v>-866.8519999999999</v>
       </c>
       <c r="F19">
-        <v>1066.512</v>
+        <v>1129.248</v>
       </c>
       <c r="G19">
         <v>490.7</v>
@@ -2851,45 +2851,45 @@
         <v>571.1</v>
       </c>
       <c r="M19">
-        <v>55.24532160000001</v>
+        <v>60.41476800000002</v>
       </c>
       <c r="N19">
-        <v>515.8546784</v>
+        <v>510.685232</v>
       </c>
       <c r="O19">
-        <v>128.65415679296</v>
+        <v>127.3648968608</v>
       </c>
       <c r="P19">
-        <v>387.20052160704</v>
+        <v>383.3203351392</v>
       </c>
       <c r="Q19">
-        <v>643.3005216070401</v>
+        <v>639.4203351392</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.079784057008181</v>
+        <v>0.08010890851594805</v>
       </c>
       <c r="T19">
-        <v>0.7848512011127253</v>
+        <v>0.7923535454029573</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.2494</v>
       </c>
       <c r="W19">
-        <v>0.03888108</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.33752693368337</v>
+        <v>9.452986726689074</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07291758298307742</v>
+        <v>0.07278769164936456</v>
       </c>
       <c r="C20">
-        <v>4931.641104226297</v>
+        <v>4881.024036060993</v>
       </c>
       <c r="D20">
-        <v>5570.189104226297</v>
+        <v>5582.308036060994</v>
       </c>
       <c r="E20">
-        <v>-866.8520000000001</v>
+        <v>-804.116</v>
       </c>
       <c r="F20">
-        <v>1129.248</v>
+        <v>1191.984</v>
       </c>
       <c r="G20">
         <v>490.7</v>
@@ -2933,28 +2933,28 @@
         <v>571.1</v>
       </c>
       <c r="M20">
-        <v>60.414768</v>
+        <v>63.77114400000001</v>
       </c>
       <c r="N20">
-        <v>510.685232</v>
+        <v>507.328856</v>
       </c>
       <c r="O20">
-        <v>127.3648968608</v>
+        <v>126.5278166864</v>
       </c>
       <c r="P20">
-        <v>383.3203351392</v>
+        <v>380.8010393136</v>
       </c>
       <c r="Q20">
-        <v>639.4203351392</v>
+        <v>636.9010393136</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08010890851594805</v>
+        <v>0.08044178104859823</v>
       </c>
       <c r="T20">
-        <v>0.7923535454029573</v>
+        <v>0.800041132762084</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.452986726689078</v>
+        <v>8.955461109494916</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07278769164936456</v>
+        <v>0.07265780031565175</v>
       </c>
       <c r="C21">
-        <v>4881.024036060993</v>
+        <v>4830.459816637879</v>
       </c>
       <c r="D21">
-        <v>5582.308036060994</v>
+        <v>5594.47981663788</v>
       </c>
       <c r="E21">
-        <v>-804.116</v>
+        <v>-741.3799999999999</v>
       </c>
       <c r="F21">
-        <v>1191.984</v>
+        <v>1254.72</v>
       </c>
       <c r="G21">
         <v>490.7</v>
@@ -3015,28 +3015,28 @@
         <v>571.1</v>
       </c>
       <c r="M21">
-        <v>63.77114400000001</v>
+        <v>67.12752000000002</v>
       </c>
       <c r="N21">
-        <v>507.328856</v>
+        <v>503.97248</v>
       </c>
       <c r="O21">
-        <v>126.5278166864</v>
+        <v>125.690736512</v>
       </c>
       <c r="P21">
-        <v>380.8010393136</v>
+        <v>378.281743488</v>
       </c>
       <c r="Q21">
-        <v>636.9010393136</v>
+        <v>634.381743488</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08044178104859823</v>
+        <v>0.08078297539456468</v>
       </c>
       <c r="T21">
-        <v>0.800041132762084</v>
+        <v>0.8079209098051889</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.955461109494916</v>
+        <v>8.507688054020168</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07265780031565175</v>
+        <v>0.07252790898193891</v>
       </c>
       <c r="C22">
-        <v>4830.459816637879</v>
+        <v>4779.948792409863</v>
       </c>
       <c r="D22">
-        <v>5594.47981663788</v>
+        <v>5606.704792409863</v>
       </c>
       <c r="E22">
-        <v>-741.3799999999999</v>
+        <v>-678.644</v>
       </c>
       <c r="F22">
-        <v>1254.72</v>
+        <v>1317.456</v>
       </c>
       <c r="G22">
         <v>490.7</v>
@@ -3097,28 +3097,28 @@
         <v>571.1</v>
       </c>
       <c r="M22">
-        <v>67.12752000000002</v>
+        <v>70.483896</v>
       </c>
       <c r="N22">
-        <v>503.97248</v>
+        <v>500.616104</v>
       </c>
       <c r="O22">
-        <v>125.690736512</v>
+        <v>124.8536563376</v>
       </c>
       <c r="P22">
-        <v>378.281743488</v>
+        <v>375.7624476624</v>
       </c>
       <c r="Q22">
-        <v>634.381743488</v>
+        <v>631.8624476624</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08078297539456468</v>
+        <v>0.08113280757207457</v>
       </c>
       <c r="T22">
-        <v>0.8079209098051889</v>
+        <v>0.8160001748747014</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.507688054020168</v>
+        <v>8.102560051447782</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07252790898193891</v>
+        <v>0.07239801764822609</v>
       </c>
       <c r="C23">
-        <v>4779.948792409863</v>
+        <v>4729.491312864732</v>
       </c>
       <c r="D23">
-        <v>5606.704792409863</v>
+        <v>5618.983312864732</v>
       </c>
       <c r="E23">
-        <v>-678.644</v>
+        <v>-615.9080000000001</v>
       </c>
       <c r="F23">
-        <v>1317.456</v>
+        <v>1380.192</v>
       </c>
       <c r="G23">
         <v>490.7</v>
@@ -3179,28 +3179,28 @@
         <v>571.1</v>
       </c>
       <c r="M23">
-        <v>70.483896</v>
+        <v>73.840272</v>
       </c>
       <c r="N23">
-        <v>500.616104</v>
+        <v>497.259728</v>
       </c>
       <c r="O23">
-        <v>124.8536563376</v>
+        <v>124.0165761632</v>
       </c>
       <c r="P23">
-        <v>375.7624476624</v>
+        <v>373.2431518368</v>
       </c>
       <c r="Q23">
-        <v>631.8624476624</v>
+        <v>629.3431518368</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08113280757207457</v>
+        <v>0.08149160980541806</v>
       </c>
       <c r="T23">
-        <v>0.8160001748747014</v>
+        <v>0.824286600587022</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.102560051447782</v>
+        <v>7.734261867291063</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07239801764822609</v>
+        <v>0.07240623671451324</v>
       </c>
       <c r="C24">
-        <v>4729.491312864732</v>
+        <v>4665.976777724569</v>
       </c>
       <c r="D24">
-        <v>5618.983312864732</v>
+        <v>5618.204777724569</v>
       </c>
       <c r="E24">
-        <v>-615.9080000000001</v>
+        <v>-553.172</v>
       </c>
       <c r="F24">
-        <v>1380.192</v>
+        <v>1442.928</v>
       </c>
       <c r="G24">
         <v>490.7</v>
@@ -3261,45 +3261,45 @@
         <v>571.1</v>
       </c>
       <c r="M24">
-        <v>73.840272</v>
+        <v>78.3509904</v>
       </c>
       <c r="N24">
-        <v>497.259728</v>
+        <v>492.7490096</v>
       </c>
       <c r="O24">
-        <v>124.0165761632</v>
+        <v>122.89160299424</v>
       </c>
       <c r="P24">
-        <v>373.2431518368</v>
+        <v>369.85740660576</v>
       </c>
       <c r="Q24">
-        <v>629.3431518368</v>
+        <v>625.9574066057601</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08149160980541806</v>
+        <v>0.08185973157728993</v>
       </c>
       <c r="T24">
-        <v>0.824286600587022</v>
+        <v>0.8327882581360262</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.2494</v>
       </c>
       <c r="W24">
-        <v>0.04015709999999999</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.734261867291063</v>
+        <v>7.28899529009655</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07240623671451324</v>
+        <v>0.07228235018080043</v>
       </c>
       <c r="C25">
-        <v>4665.976777724569</v>
+        <v>4614.998619387297</v>
       </c>
       <c r="D25">
-        <v>5618.204777724569</v>
+        <v>5629.962619387298</v>
       </c>
       <c r="E25">
-        <v>-553.172</v>
+        <v>-490.4359999999999</v>
       </c>
       <c r="F25">
-        <v>1442.928</v>
+        <v>1505.664</v>
       </c>
       <c r="G25">
         <v>490.7</v>
@@ -3343,28 +3343,28 @@
         <v>571.1</v>
       </c>
       <c r="M25">
-        <v>78.3509904</v>
+        <v>81.75755520000001</v>
       </c>
       <c r="N25">
-        <v>492.7490096</v>
+        <v>489.3424448</v>
       </c>
       <c r="O25">
-        <v>122.89160299424</v>
+        <v>122.04200573312</v>
       </c>
       <c r="P25">
-        <v>369.85740660576</v>
+        <v>367.30043906688</v>
       </c>
       <c r="Q25">
-        <v>625.9574066057601</v>
+        <v>623.40043906688</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08185973157728993</v>
+        <v>0.08223754076421108</v>
       </c>
       <c r="T25">
-        <v>0.8327882581360262</v>
+        <v>0.8415136435152674</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.28899529009655</v>
+        <v>6.985287153009192</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07228235018080043</v>
+        <v>0.07215846364708758</v>
       </c>
       <c r="C26">
-        <v>4614.998619387298</v>
+        <v>4564.069778145918</v>
       </c>
       <c r="D26">
-        <v>5629.962619387298</v>
+        <v>5641.769778145918</v>
       </c>
       <c r="E26">
-        <v>-490.4360000000001</v>
+        <v>-427.7</v>
       </c>
       <c r="F26">
-        <v>1505.664</v>
+        <v>1568.4</v>
       </c>
       <c r="G26">
         <v>490.7</v>
@@ -3425,28 +3425,28 @@
         <v>571.1</v>
       </c>
       <c r="M26">
-        <v>81.7575552</v>
+        <v>85.16412000000001</v>
       </c>
       <c r="N26">
-        <v>489.3424448</v>
+        <v>485.93588</v>
       </c>
       <c r="O26">
-        <v>122.04200573312</v>
+        <v>121.192408472</v>
       </c>
       <c r="P26">
-        <v>367.30043906688</v>
+        <v>364.743471528</v>
       </c>
       <c r="Q26">
-        <v>623.40043906688</v>
+        <v>620.843471528</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08223754076421108</v>
+        <v>0.08262542486278344</v>
       </c>
       <c r="T26">
-        <v>0.8415136435152674</v>
+        <v>0.8504717058379548</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.985287153009194</v>
+        <v>6.705875666888825</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07215846364708758</v>
+        <v>0.07203457711337474</v>
       </c>
       <c r="C27">
-        <v>4564.069778145918</v>
+        <v>4513.19056493599</v>
       </c>
       <c r="D27">
-        <v>5641.769778145918</v>
+        <v>5653.62656493599</v>
       </c>
       <c r="E27">
-        <v>-427.7</v>
+        <v>-364.9639999999999</v>
       </c>
       <c r="F27">
-        <v>1568.4</v>
+        <v>1631.136</v>
       </c>
       <c r="G27">
         <v>490.7</v>
@@ -3507,28 +3507,28 @@
         <v>571.1</v>
       </c>
       <c r="M27">
-        <v>85.16412000000001</v>
+        <v>88.57068480000001</v>
       </c>
       <c r="N27">
-        <v>485.93588</v>
+        <v>482.5293152</v>
       </c>
       <c r="O27">
-        <v>121.192408472</v>
+        <v>120.34281121088</v>
       </c>
       <c r="P27">
-        <v>364.743471528</v>
+        <v>362.18650398912</v>
       </c>
       <c r="Q27">
-        <v>620.843471528</v>
+        <v>618.2865039891201</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08262542486278344</v>
+        <v>0.08302379231537128</v>
       </c>
       <c r="T27">
-        <v>0.8504717058379548</v>
+        <v>0.8596718779531475</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.705875666888825</v>
+        <v>6.447957372008486</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07203457711337474</v>
+        <v>0.07191069057966193</v>
       </c>
       <c r="C28">
-        <v>4513.19056493599</v>
+        <v>4462.361293312439</v>
       </c>
       <c r="D28">
-        <v>5653.62656493599</v>
+        <v>5665.533293312439</v>
       </c>
       <c r="E28">
-        <v>-364.9639999999999</v>
+        <v>-302.2279999999998</v>
       </c>
       <c r="F28">
-        <v>1631.136</v>
+        <v>1693.872</v>
       </c>
       <c r="G28">
         <v>490.7</v>
@@ -3589,28 +3589,28 @@
         <v>571.1</v>
       </c>
       <c r="M28">
-        <v>88.57068480000001</v>
+        <v>91.97724960000002</v>
       </c>
       <c r="N28">
-        <v>482.5293152</v>
+        <v>479.1227504</v>
       </c>
       <c r="O28">
-        <v>120.34281121088</v>
+        <v>119.49321394976</v>
       </c>
       <c r="P28">
-        <v>362.18650398912</v>
+        <v>359.62953645024</v>
       </c>
       <c r="Q28">
-        <v>618.2865039891201</v>
+        <v>615.7295364502399</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08302379231537128</v>
+        <v>0.08343307394474236</v>
       </c>
       <c r="T28">
-        <v>0.8596718779531475</v>
+        <v>0.8691241095783454</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.447957372008486</v>
+        <v>6.20914413600817</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07191069057966193</v>
+        <v>0.07199697204594908</v>
       </c>
       <c r="C29">
-        <v>4462.361293312439</v>
+        <v>4391.327492603151</v>
       </c>
       <c r="D29">
-        <v>5665.533293312439</v>
+        <v>5657.235492603151</v>
       </c>
       <c r="E29">
-        <v>-302.2279999999998</v>
+        <v>-239.492</v>
       </c>
       <c r="F29">
-        <v>1693.872</v>
+        <v>1756.608</v>
       </c>
       <c r="G29">
         <v>490.7</v>
@@ -3671,45 +3671,45 @@
         <v>571.1</v>
       </c>
       <c r="M29">
-        <v>91.97724960000002</v>
+        <v>97.14042240000002</v>
       </c>
       <c r="N29">
-        <v>479.1227504</v>
+        <v>473.9595776</v>
       </c>
       <c r="O29">
-        <v>119.49321394976</v>
+        <v>118.20551865344</v>
       </c>
       <c r="P29">
-        <v>359.62953645024</v>
+        <v>355.75405894656</v>
       </c>
       <c r="Q29">
-        <v>615.7295364502399</v>
+        <v>611.85405894656</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08343307394474236</v>
+        <v>0.08385372450826262</v>
       </c>
       <c r="T29">
-        <v>0.8691241095783454</v>
+        <v>0.8788389031931322</v>
       </c>
       <c r="U29">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.2494</v>
       </c>
       <c r="W29">
-        <v>0.04075757999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.20914413600817</v>
+        <v>5.87911793968069</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07199697204594908</v>
+        <v>0.07188059151223625</v>
       </c>
       <c r="C30">
-        <v>4391.327492603151</v>
+        <v>4339.789689569646</v>
       </c>
       <c r="D30">
-        <v>5657.235492603151</v>
+        <v>5668.433689569646</v>
       </c>
       <c r="E30">
-        <v>-239.492</v>
+        <v>-176.7559999999999</v>
       </c>
       <c r="F30">
-        <v>1756.608</v>
+        <v>1819.344</v>
       </c>
       <c r="G30">
         <v>490.7</v>
@@ -3753,28 +3753,28 @@
         <v>571.1</v>
       </c>
       <c r="M30">
-        <v>97.14042240000002</v>
+        <v>100.6097232</v>
       </c>
       <c r="N30">
-        <v>473.9595776</v>
+        <v>470.4902768</v>
       </c>
       <c r="O30">
-        <v>118.20551865344</v>
+        <v>117.34027503392</v>
       </c>
       <c r="P30">
-        <v>355.75405894656</v>
+        <v>353.15000176608</v>
       </c>
       <c r="Q30">
-        <v>611.85405894656</v>
+        <v>609.25000176608</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08385372450826262</v>
+        <v>0.08428622438343135</v>
       </c>
       <c r="T30">
-        <v>0.8788389031931322</v>
+        <v>0.8888273529660821</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.87911793968069</v>
+        <v>5.676389734864114</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07188059151223625</v>
+        <v>0.07176421097852342</v>
       </c>
       <c r="C31">
-        <v>4339.789689569646</v>
+        <v>4288.296306935345</v>
       </c>
       <c r="D31">
-        <v>5668.433689569646</v>
+        <v>5679.676306935346</v>
       </c>
       <c r="E31">
-        <v>-176.7560000000001</v>
+        <v>-114.0200000000002</v>
       </c>
       <c r="F31">
-        <v>1819.344</v>
+        <v>1882.08</v>
       </c>
       <c r="G31">
         <v>490.7</v>
@@ -3835,28 +3835,28 @@
         <v>571.1</v>
       </c>
       <c r="M31">
-        <v>100.6097232</v>
+        <v>104.079024</v>
       </c>
       <c r="N31">
-        <v>470.4902768</v>
+        <v>467.020976</v>
       </c>
       <c r="O31">
-        <v>117.34027503392</v>
+        <v>116.4750314144</v>
       </c>
       <c r="P31">
-        <v>353.15000176608</v>
+        <v>350.5459445856</v>
       </c>
       <c r="Q31">
-        <v>609.25000176608</v>
+        <v>606.6459445856001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08428622438343135</v>
+        <v>0.08473108139789061</v>
       </c>
       <c r="T31">
-        <v>0.888827352966082</v>
+        <v>0.8991011870182589</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.676389734864115</v>
+        <v>5.487176743701978</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07176421097852342</v>
+        <v>0.07164783044481059</v>
       </c>
       <c r="C32">
-        <v>4288.296306935345</v>
+        <v>4236.847609532151</v>
       </c>
       <c r="D32">
-        <v>5679.676306935346</v>
+        <v>5690.963609532151</v>
       </c>
       <c r="E32">
-        <v>-114.0200000000002</v>
+        <v>-51.28400000000011</v>
       </c>
       <c r="F32">
-        <v>1882.08</v>
+        <v>1944.816</v>
       </c>
       <c r="G32">
         <v>490.7</v>
@@ -3917,28 +3917,28 @@
         <v>571.1</v>
       </c>
       <c r="M32">
-        <v>104.079024</v>
+        <v>107.5483248</v>
       </c>
       <c r="N32">
-        <v>467.020976</v>
+        <v>463.5516752</v>
       </c>
       <c r="O32">
-        <v>116.4750314144</v>
+        <v>115.60978779488</v>
       </c>
       <c r="P32">
-        <v>350.5459445856</v>
+        <v>347.94188740512</v>
       </c>
       <c r="Q32">
-        <v>606.6459445856001</v>
+        <v>604.0418874051201</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08473108139789061</v>
+        <v>0.08518883281856608</v>
       </c>
       <c r="T32">
-        <v>0.8991011870182589</v>
+        <v>0.9096728133618033</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.487176743701978</v>
+        <v>5.310171042292237</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07164783044481059</v>
+        <v>0.07153144991109776</v>
       </c>
       <c r="C33">
-        <v>4236.847609532151</v>
+        <v>4185.443864301367</v>
       </c>
       <c r="D33">
-        <v>5690.963609532151</v>
+        <v>5702.295864301367</v>
       </c>
       <c r="E33">
-        <v>-51.28400000000011</v>
+        <v>11.452</v>
       </c>
       <c r="F33">
-        <v>1944.816</v>
+        <v>2007.552</v>
       </c>
       <c r="G33">
         <v>490.7</v>
@@ -3999,28 +3999,28 @@
         <v>571.1</v>
       </c>
       <c r="M33">
-        <v>107.5483248</v>
+        <v>111.0176256</v>
       </c>
       <c r="N33">
-        <v>463.5516752</v>
+        <v>460.0823744</v>
       </c>
       <c r="O33">
-        <v>115.60978779488</v>
+        <v>114.74454417536</v>
       </c>
       <c r="P33">
-        <v>347.94188740512</v>
+        <v>345.33783022464</v>
       </c>
       <c r="Q33">
-        <v>604.0418874051201</v>
+        <v>601.43783022464</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08518883281856608</v>
+        <v>0.08566004751632024</v>
       </c>
       <c r="T33">
-        <v>0.9096728133618033</v>
+        <v>0.9205553698919224</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.310171042292237</v>
+        <v>5.144228197220603</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07153144991109776</v>
+        <v>0.07141506937738493</v>
       </c>
       <c r="C34">
-        <v>4185.443864301367</v>
+        <v>4134.085340314758</v>
       </c>
       <c r="D34">
-        <v>5702.295864301367</v>
+        <v>5713.673340314757</v>
       </c>
       <c r="E34">
-        <v>11.452</v>
+        <v>74.18799999999987</v>
       </c>
       <c r="F34">
-        <v>2007.552</v>
+        <v>2070.288</v>
       </c>
       <c r="G34">
         <v>490.7</v>
@@ -4081,28 +4081,28 @@
         <v>571.1</v>
       </c>
       <c r="M34">
-        <v>111.0176256</v>
+        <v>114.4869264</v>
       </c>
       <c r="N34">
-        <v>460.0823744</v>
+        <v>456.6130736</v>
       </c>
       <c r="O34">
-        <v>114.74454417536</v>
+        <v>113.87930055584</v>
       </c>
       <c r="P34">
-        <v>345.33783022464</v>
+        <v>342.73377304416</v>
       </c>
       <c r="Q34">
-        <v>601.43783022464</v>
+        <v>598.83377304416</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08566004751632024</v>
+        <v>0.08614532832445512</v>
       </c>
       <c r="T34">
-        <v>0.9205553698919224</v>
+        <v>0.9317627788557765</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.144228197220603</v>
+        <v>4.988342494274525</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07141506937738493</v>
+        <v>0.07129868884367209</v>
       </c>
       <c r="C35">
-        <v>4134.085340314758</v>
+        <v>4082.772308795832</v>
       </c>
       <c r="D35">
-        <v>5713.673340314757</v>
+        <v>5725.096308795833</v>
       </c>
       <c r="E35">
-        <v>74.18799999999987</v>
+        <v>136.9240000000002</v>
       </c>
       <c r="F35">
-        <v>2070.288</v>
+        <v>2133.024</v>
       </c>
       <c r="G35">
         <v>490.7</v>
@@ -4163,28 +4163,28 @@
         <v>571.1</v>
       </c>
       <c r="M35">
-        <v>114.4869264</v>
+        <v>117.9562272</v>
       </c>
       <c r="N35">
-        <v>456.6130736</v>
+        <v>453.1437728</v>
       </c>
       <c r="O35">
-        <v>113.87930055584</v>
+        <v>113.01405693632</v>
       </c>
       <c r="P35">
-        <v>342.73377304416</v>
+        <v>340.12971586368</v>
       </c>
       <c r="Q35">
-        <v>598.83377304416</v>
+        <v>596.22971586368</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08614532832445512</v>
+        <v>0.08664531461162439</v>
       </c>
       <c r="T35">
-        <v>0.9317627788557765</v>
+        <v>0.9433098062730807</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.988342494274525</v>
+        <v>4.841626538560567</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07129868884367209</v>
+        <v>0.07118230830995927</v>
       </c>
       <c r="C36">
-        <v>4082.772308795832</v>
+        <v>4031.505043141401</v>
       </c>
       <c r="D36">
-        <v>5725.096308795833</v>
+        <v>5736.565043141401</v>
       </c>
       <c r="E36">
-        <v>136.9240000000002</v>
+        <v>199.6600000000001</v>
       </c>
       <c r="F36">
-        <v>2133.024</v>
+        <v>2195.76</v>
       </c>
       <c r="G36">
         <v>490.7</v>
@@ -4245,28 +4245,28 @@
         <v>571.1</v>
       </c>
       <c r="M36">
-        <v>117.9562272</v>
+        <v>121.425528</v>
       </c>
       <c r="N36">
-        <v>453.1437728</v>
+        <v>449.674472</v>
       </c>
       <c r="O36">
-        <v>113.01405693632</v>
+        <v>112.1488133168</v>
       </c>
       <c r="P36">
-        <v>340.12971586368</v>
+        <v>337.5256586832</v>
       </c>
       <c r="Q36">
-        <v>596.22971586368</v>
+        <v>593.6256586832001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08664531461162439</v>
+        <v>0.08716068509224503</v>
       </c>
       <c r="T36">
-        <v>0.9433098062730807</v>
+        <v>0.9552121268416867</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.841626538560567</v>
+        <v>4.703294351744552</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07118230830995927</v>
+        <v>0.07106592777624643</v>
       </c>
       <c r="C37">
-        <v>4031.505043141401</v>
+        <v>3980.283818943393</v>
       </c>
       <c r="D37">
-        <v>5736.565043141401</v>
+        <v>5748.079818943394</v>
       </c>
       <c r="E37">
-        <v>199.6600000000001</v>
+        <v>262.3960000000004</v>
       </c>
       <c r="F37">
-        <v>2195.76</v>
+        <v>2258.496000000001</v>
       </c>
       <c r="G37">
         <v>490.7</v>
@@ -4327,28 +4327,28 @@
         <v>571.1</v>
       </c>
       <c r="M37">
-        <v>121.425528</v>
+        <v>124.8948288</v>
       </c>
       <c r="N37">
-        <v>449.674472</v>
+        <v>446.2051712</v>
       </c>
       <c r="O37">
-        <v>112.1488133168</v>
+        <v>111.28356969728</v>
       </c>
       <c r="P37">
-        <v>337.5256586832</v>
+        <v>334.92160150272</v>
       </c>
       <c r="Q37">
-        <v>593.6256586832001</v>
+        <v>591.02160150272</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08716068509224503</v>
+        <v>0.08769216090038506</v>
       </c>
       <c r="T37">
-        <v>0.9552121268416867</v>
+        <v>0.9674863949280614</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.703294351744552</v>
+        <v>4.572647286418313</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07106592777624644</v>
+        <v>0.07164385224253361</v>
       </c>
       <c r="C38">
-        <v>3980.283818943392</v>
+        <v>3860.81823317789</v>
       </c>
       <c r="D38">
-        <v>5748.079818943393</v>
+        <v>5691.35023317789</v>
       </c>
       <c r="E38">
-        <v>262.396</v>
+        <v>325.1319999999998</v>
       </c>
       <c r="F38">
-        <v>2258.496</v>
+        <v>2321.232</v>
       </c>
       <c r="G38">
         <v>490.7</v>
@@ -4409,45 +4409,45 @@
         <v>571.1</v>
       </c>
       <c r="M38">
-        <v>124.8948288</v>
+        <v>134.1672096</v>
       </c>
       <c r="N38">
-        <v>446.2051712</v>
+        <v>436.9327904</v>
       </c>
       <c r="O38">
-        <v>111.28356969728</v>
+        <v>108.97103792576</v>
       </c>
       <c r="P38">
-        <v>334.92160150272</v>
+        <v>327.96175247424</v>
       </c>
       <c r="Q38">
-        <v>591.02160150272</v>
+        <v>584.0617524742401</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08769216090038506</v>
+        <v>0.08824050895640255</v>
       </c>
       <c r="T38">
-        <v>0.9674863949280614</v>
+        <v>0.9801503223187655</v>
       </c>
       <c r="U38">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.2494</v>
       </c>
       <c r="W38">
-        <v>0.04150818</v>
+        <v>0.04338468</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.572647286418315</v>
+        <v>4.256628737399037</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07164385224253361</v>
+        <v>0.07154623670882077</v>
       </c>
       <c r="C39">
-        <v>3860.81823317789</v>
+        <v>3807.585535778624</v>
       </c>
       <c r="D39">
-        <v>5691.35023317789</v>
+        <v>5700.853535778625</v>
       </c>
       <c r="E39">
-        <v>325.1319999999998</v>
+        <v>387.8680000000002</v>
       </c>
       <c r="F39">
-        <v>2321.232</v>
+        <v>2383.968</v>
       </c>
       <c r="G39">
         <v>490.7</v>
@@ -4491,28 +4491,28 @@
         <v>571.1</v>
       </c>
       <c r="M39">
-        <v>134.1672096</v>
+        <v>137.7933504</v>
       </c>
       <c r="N39">
-        <v>436.9327904</v>
+        <v>433.3066496</v>
       </c>
       <c r="O39">
-        <v>108.97103792576</v>
+        <v>108.06667841024</v>
       </c>
       <c r="P39">
-        <v>327.96175247424</v>
+        <v>325.23997118976</v>
       </c>
       <c r="Q39">
-        <v>584.0617524742401</v>
+        <v>581.33997118976</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08824050895640255</v>
+        <v>0.08880654565938834</v>
       </c>
       <c r="T39">
-        <v>0.9801503223187655</v>
+        <v>0.9932227634962666</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.256628737399037</v>
+        <v>4.144612191678009</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07154623670882077</v>
+        <v>0.07144862117510795</v>
       </c>
       <c r="C40">
-        <v>3807.585535778624</v>
+        <v>3754.384628310141</v>
       </c>
       <c r="D40">
-        <v>5700.853535778625</v>
+        <v>5710.388628310141</v>
       </c>
       <c r="E40">
-        <v>387.8680000000002</v>
+        <v>450.604</v>
       </c>
       <c r="F40">
-        <v>2383.968</v>
+        <v>2446.704</v>
       </c>
       <c r="G40">
         <v>490.7</v>
@@ -4573,28 +4573,28 @@
         <v>571.1</v>
       </c>
       <c r="M40">
-        <v>137.7933504</v>
+        <v>141.4194912</v>
       </c>
       <c r="N40">
-        <v>433.3066496</v>
+        <v>429.6805088</v>
       </c>
       <c r="O40">
-        <v>108.06667841024</v>
+        <v>107.16231889472</v>
       </c>
       <c r="P40">
-        <v>325.23997118976</v>
+        <v>322.51818990528</v>
       </c>
       <c r="Q40">
-        <v>581.33997118976</v>
+        <v>578.61818990528</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08880654565938834</v>
+        <v>0.0893911409427999</v>
       </c>
       <c r="T40">
-        <v>0.9932227634962666</v>
+        <v>1.006723809302538</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.144612191678009</v>
+        <v>4.038340084199087</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07144862117510795</v>
+        <v>0.07240184564139511</v>
       </c>
       <c r="C41">
-        <v>3754.384628310141</v>
+        <v>3599.880686780824</v>
       </c>
       <c r="D41">
-        <v>5710.388628310141</v>
+        <v>5618.620686780825</v>
       </c>
       <c r="E41">
-        <v>450.604</v>
+        <v>513.3400000000004</v>
       </c>
       <c r="F41">
-        <v>2446.704</v>
+        <v>2509.440000000001</v>
       </c>
       <c r="G41">
         <v>490.7</v>
@@ -4655,45 +4655,45 @@
         <v>571.1</v>
       </c>
       <c r="M41">
-        <v>141.4194912</v>
+        <v>153.828672</v>
       </c>
       <c r="N41">
-        <v>429.6805088</v>
+        <v>417.271328</v>
       </c>
       <c r="O41">
-        <v>107.16231889472</v>
+        <v>104.0674692032</v>
       </c>
       <c r="P41">
-        <v>322.51818990528</v>
+        <v>313.2038587968</v>
       </c>
       <c r="Q41">
-        <v>578.61818990528</v>
+        <v>569.3038587968</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0893911409427999</v>
+        <v>0.08999522273565852</v>
       </c>
       <c r="T41">
-        <v>1.006723809302538</v>
+        <v>1.020674889969019</v>
       </c>
       <c r="U41">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V41">
         <v>0.2494</v>
       </c>
       <c r="W41">
-        <v>0.04338468</v>
+        <v>0.04601178</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.038340084199087</v>
+        <v>3.712571866966386</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07240184564139511</v>
+        <v>0.07233050110768227</v>
       </c>
       <c r="C42">
-        <v>3599.880686780824</v>
+        <v>3543.910862026413</v>
       </c>
       <c r="D42">
-        <v>5618.620686780825</v>
+        <v>5625.386862026414</v>
       </c>
       <c r="E42">
-        <v>513.3400000000004</v>
+        <v>576.0760000000002</v>
       </c>
       <c r="F42">
-        <v>2509.440000000001</v>
+        <v>2572.176</v>
       </c>
       <c r="G42">
         <v>490.7</v>
@@ -4737,28 +4737,28 @@
         <v>571.1</v>
       </c>
       <c r="M42">
-        <v>153.828672</v>
+        <v>157.6743888</v>
       </c>
       <c r="N42">
-        <v>417.271328</v>
+        <v>413.4256112</v>
       </c>
       <c r="O42">
-        <v>104.0674692032</v>
+        <v>103.10834743328</v>
       </c>
       <c r="P42">
-        <v>313.2038587968</v>
+        <v>310.31726376672</v>
       </c>
       <c r="Q42">
-        <v>569.3038587968</v>
+        <v>566.41726376672</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08999522273565852</v>
+        <v>0.09061978187742759</v>
       </c>
       <c r="T42">
-        <v>1.020674889969019</v>
+        <v>1.035098888624194</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.712571866966386</v>
+        <v>3.622021333625743</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07233050110768227</v>
+        <v>0.07225915657396945</v>
       </c>
       <c r="C43">
-        <v>3543.910862026413</v>
+        <v>3487.957353135984</v>
       </c>
       <c r="D43">
-        <v>5625.386862026414</v>
+        <v>5632.169353135984</v>
       </c>
       <c r="E43">
-        <v>576.0760000000002</v>
+        <v>638.8120000000001</v>
       </c>
       <c r="F43">
-        <v>2572.176</v>
+        <v>2634.912</v>
       </c>
       <c r="G43">
         <v>490.7</v>
@@ -4819,28 +4819,28 @@
         <v>571.1</v>
       </c>
       <c r="M43">
-        <v>157.6743888</v>
+        <v>161.5201056</v>
       </c>
       <c r="N43">
-        <v>413.4256112</v>
+        <v>409.5798944</v>
       </c>
       <c r="O43">
-        <v>103.10834743328</v>
+        <v>102.14922566336</v>
       </c>
       <c r="P43">
-        <v>310.31726376672</v>
+        <v>307.43066873664</v>
       </c>
       <c r="Q43">
-        <v>566.41726376672</v>
+        <v>563.53066873664</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09061978187742759</v>
+        <v>0.09126587754132663</v>
       </c>
       <c r="T43">
-        <v>1.035098888624194</v>
+        <v>1.05002026654334</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.622021333625743</v>
+        <v>3.535782730444178</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07225915657396945</v>
+        <v>0.07309153444025662</v>
       </c>
       <c r="C44">
-        <v>3487.957353135984</v>
+        <v>3347.093519860589</v>
       </c>
       <c r="D44">
-        <v>5632.169353135984</v>
+        <v>5554.04151986059</v>
       </c>
       <c r="E44">
-        <v>638.8120000000001</v>
+        <v>701.548</v>
       </c>
       <c r="F44">
-        <v>2634.912</v>
+        <v>2697.648</v>
       </c>
       <c r="G44">
         <v>490.7</v>
@@ -4901,45 +4901,45 @@
         <v>571.1</v>
       </c>
       <c r="M44">
-        <v>161.5201056</v>
+        <v>172.9192368</v>
       </c>
       <c r="N44">
-        <v>409.5798944</v>
+        <v>398.1807632</v>
       </c>
       <c r="O44">
-        <v>102.14922566336</v>
+        <v>99.30628234208001</v>
       </c>
       <c r="P44">
-        <v>307.43066873664</v>
+        <v>298.87448085792</v>
       </c>
       <c r="Q44">
-        <v>563.53066873664</v>
+        <v>554.9744808579201</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09126587754132663</v>
+        <v>0.09193464322852038</v>
       </c>
       <c r="T44">
-        <v>1.05002026654334</v>
+        <v>1.065465201582457</v>
       </c>
       <c r="U44">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V44">
         <v>0.2494</v>
       </c>
       <c r="W44">
-        <v>0.04601178</v>
+        <v>0.04811346</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.535782730444178</v>
+        <v>3.302697898560237</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07309153444025662</v>
+        <v>0.07304120670654379</v>
       </c>
       <c r="C45">
-        <v>3347.093519860589</v>
+        <v>3289.019715053751</v>
       </c>
       <c r="D45">
-        <v>5554.04151986059</v>
+        <v>5558.703715053751</v>
       </c>
       <c r="E45">
-        <v>701.548</v>
+        <v>764.2839999999999</v>
       </c>
       <c r="F45">
-        <v>2697.648</v>
+        <v>2760.384</v>
       </c>
       <c r="G45">
         <v>490.7</v>
@@ -4983,28 +4983,28 @@
         <v>571.1</v>
       </c>
       <c r="M45">
-        <v>172.9192368</v>
+        <v>176.9406144</v>
       </c>
       <c r="N45">
-        <v>398.1807632</v>
+        <v>394.1593856</v>
       </c>
       <c r="O45">
-        <v>99.30628234208001</v>
+        <v>98.30335076864</v>
       </c>
       <c r="P45">
-        <v>298.87448085792</v>
+        <v>295.85603483136</v>
       </c>
       <c r="Q45">
-        <v>554.9744808579201</v>
+        <v>551.9560348313601</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09193464322852038</v>
+        <v>0.09262729340454247</v>
       </c>
       <c r="T45">
-        <v>1.065465201582457</v>
+        <v>1.081461741444399</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.302697898560237</v>
+        <v>3.227636582683868</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07304120670654379</v>
+        <v>0.07299087897283096</v>
       </c>
       <c r="C46">
-        <v>3289.019715053751</v>
+        <v>3230.953743938842</v>
       </c>
       <c r="D46">
-        <v>5558.703715053751</v>
+        <v>5563.373743938842</v>
       </c>
       <c r="E46">
-        <v>764.2839999999999</v>
+        <v>827.0200000000002</v>
       </c>
       <c r="F46">
-        <v>2760.384</v>
+        <v>2823.12</v>
       </c>
       <c r="G46">
         <v>490.7</v>
@@ -5065,28 +5065,28 @@
         <v>571.1</v>
       </c>
       <c r="M46">
-        <v>176.9406144</v>
+        <v>180.961992</v>
       </c>
       <c r="N46">
-        <v>394.1593856</v>
+        <v>390.138008</v>
       </c>
       <c r="O46">
-        <v>98.30335076864</v>
+        <v>97.30041919520001</v>
       </c>
       <c r="P46">
-        <v>295.85603483136</v>
+        <v>292.8375888048</v>
       </c>
       <c r="Q46">
-        <v>551.9560348313601</v>
+        <v>548.9375888048</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09262729340454247</v>
+        <v>0.09334513085969265</v>
       </c>
       <c r="T46">
-        <v>1.081461741444399</v>
+        <v>1.098039973664957</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.227636582683868</v>
+        <v>3.155911325290893</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07299087897283096</v>
+        <v>0.07294055123911813</v>
       </c>
       <c r="C47">
-        <v>3230.953743938842</v>
+        <v>3172.895626276405</v>
       </c>
       <c r="D47">
-        <v>5563.373743938842</v>
+        <v>5568.051626276405</v>
       </c>
       <c r="E47">
-        <v>827.0200000000002</v>
+        <v>889.7560000000001</v>
       </c>
       <c r="F47">
-        <v>2823.12</v>
+        <v>2885.856</v>
       </c>
       <c r="G47">
         <v>490.7</v>
@@ -5147,28 +5147,28 @@
         <v>571.1</v>
       </c>
       <c r="M47">
-        <v>180.961992</v>
+        <v>184.9833696</v>
       </c>
       <c r="N47">
-        <v>390.138008</v>
+        <v>386.1166304</v>
       </c>
       <c r="O47">
-        <v>97.30041919520001</v>
+        <v>96.29748762176</v>
       </c>
       <c r="P47">
-        <v>292.8375888048</v>
+        <v>289.81914277824</v>
       </c>
       <c r="Q47">
-        <v>548.9375888048</v>
+        <v>545.91914277824</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09334513085969265</v>
+        <v>0.09408955488725579</v>
       </c>
       <c r="T47">
-        <v>1.098039973664957</v>
+        <v>1.115232214486277</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.155911325290893</v>
+        <v>3.087304557349786</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07294055123911813</v>
+        <v>0.07289022350540529</v>
       </c>
       <c r="C48">
-        <v>3172.895626276405</v>
+        <v>3114.845381893496</v>
       </c>
       <c r="D48">
-        <v>5568.051626276405</v>
+        <v>5572.737381893497</v>
       </c>
       <c r="E48">
-        <v>889.7560000000001</v>
+        <v>952.4920000000004</v>
       </c>
       <c r="F48">
-        <v>2885.856</v>
+        <v>2948.592000000001</v>
       </c>
       <c r="G48">
         <v>490.7</v>
@@ -5229,28 +5229,28 @@
         <v>571.1</v>
       </c>
       <c r="M48">
-        <v>184.9833696</v>
+        <v>189.0047472000001</v>
       </c>
       <c r="N48">
-        <v>386.1166304</v>
+        <v>382.0952528</v>
       </c>
       <c r="O48">
-        <v>96.29748762176</v>
+        <v>95.29455604831999</v>
       </c>
       <c r="P48">
-        <v>289.81914277824</v>
+        <v>286.80069675168</v>
       </c>
       <c r="Q48">
-        <v>545.91914277824</v>
+        <v>542.90069675168</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09408955488725579</v>
+        <v>0.09486207038755715</v>
       </c>
       <c r="T48">
-        <v>1.115232214486277</v>
+        <v>1.133073219112174</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.087304557349786</v>
+        <v>3.021617226342344</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07289022350540529</v>
+        <v>0.07565014217169247</v>
       </c>
       <c r="C49">
-        <v>3114.845381893496</v>
+        <v>2806.276376056762</v>
       </c>
       <c r="D49">
-        <v>5572.737381893497</v>
+        <v>5326.904376056763</v>
       </c>
       <c r="E49">
-        <v>952.4920000000004</v>
+        <v>1015.228</v>
       </c>
       <c r="F49">
-        <v>2948.592000000001</v>
+        <v>3011.328</v>
       </c>
       <c r="G49">
         <v>490.7</v>
@@ -5311,45 +5311,45 @@
         <v>571.1</v>
       </c>
       <c r="M49">
-        <v>189.0047472000001</v>
+        <v>216.5144832000001</v>
       </c>
       <c r="N49">
-        <v>382.0952528</v>
+        <v>354.5855167999999</v>
       </c>
       <c r="O49">
-        <v>95.29455604831999</v>
+        <v>88.43362788991999</v>
       </c>
       <c r="P49">
-        <v>286.80069675168</v>
+        <v>266.1518889100799</v>
       </c>
       <c r="Q49">
-        <v>542.90069675168</v>
+        <v>522.25188891008</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09486207038755715</v>
+        <v>0.09566429802248549</v>
       </c>
       <c r="T49">
-        <v>1.133073219112174</v>
+        <v>1.151600416223683</v>
       </c>
       <c r="U49">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V49">
         <v>0.2494</v>
       </c>
       <c r="W49">
-        <v>0.04811346</v>
+        <v>0.05396814</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.021617226342344</v>
+        <v>2.637698834550759</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07565014217169246</v>
+        <v>0.07565836123797963</v>
       </c>
       <c r="C50">
-        <v>2806.276376056764</v>
+        <v>2742.840669949604</v>
       </c>
       <c r="D50">
-        <v>5326.904376056764</v>
+        <v>5326.204669949605</v>
       </c>
       <c r="E50">
-        <v>1015.228</v>
+        <v>1077.964</v>
       </c>
       <c r="F50">
-        <v>3011.328</v>
+        <v>3074.064</v>
       </c>
       <c r="G50">
         <v>490.7</v>
@@ -5393,28 +5393,28 @@
         <v>571.1</v>
       </c>
       <c r="M50">
-        <v>216.5144832</v>
+        <v>221.0252016</v>
       </c>
       <c r="N50">
-        <v>354.5855168000001</v>
+        <v>350.0747984</v>
       </c>
       <c r="O50">
-        <v>88.43362788992002</v>
+        <v>87.30865472095999</v>
       </c>
       <c r="P50">
-        <v>266.1518889100801</v>
+        <v>262.7661436790399</v>
       </c>
       <c r="Q50">
-        <v>522.2518889100801</v>
+        <v>518.86614367904</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09566429802248549</v>
+        <v>0.09649798556466593</v>
       </c>
       <c r="T50">
-        <v>1.151600416223683</v>
+        <v>1.170854170084664</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.637698834550759</v>
+        <v>2.58386824609054</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07565836123797963</v>
+        <v>0.07566658030426679</v>
       </c>
       <c r="C51">
-        <v>2742.840669949604</v>
+        <v>2679.405147635622</v>
       </c>
       <c r="D51">
-        <v>5326.204669949605</v>
+        <v>5325.505147635622</v>
       </c>
       <c r="E51">
-        <v>1077.964</v>
+        <v>1140.7</v>
       </c>
       <c r="F51">
-        <v>3074.064</v>
+        <v>3136.8</v>
       </c>
       <c r="G51">
         <v>490.7</v>
@@ -5475,28 +5475,28 @@
         <v>571.1</v>
       </c>
       <c r="M51">
-        <v>221.0252016</v>
+        <v>225.53592</v>
       </c>
       <c r="N51">
-        <v>350.0747984</v>
+        <v>345.56408</v>
       </c>
       <c r="O51">
-        <v>87.30865472095999</v>
+        <v>86.183681552</v>
       </c>
       <c r="P51">
-        <v>262.7661436790399</v>
+        <v>259.380398448</v>
       </c>
       <c r="Q51">
-        <v>518.86614367904</v>
+        <v>515.480398448</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09649798556466593</v>
+        <v>0.0973650206085336</v>
       </c>
       <c r="T51">
-        <v>1.170854170084664</v>
+        <v>1.190878074100083</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.58386824609054</v>
+        <v>2.532190881168729</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07566658030426679</v>
+        <v>0.07716774277055397</v>
       </c>
       <c r="C52">
-        <v>2679.405147635622</v>
+        <v>2491.914998998981</v>
       </c>
       <c r="D52">
-        <v>5325.505147635622</v>
+        <v>5200.750998998981</v>
       </c>
       <c r="E52">
-        <v>1140.7</v>
+        <v>1203.436</v>
       </c>
       <c r="F52">
-        <v>3136.8</v>
+        <v>3199.536</v>
       </c>
       <c r="G52">
         <v>490.7</v>
@@ -5557,45 +5557,45 @@
         <v>571.1</v>
       </c>
       <c r="M52">
-        <v>225.53592</v>
+        <v>242.5248288</v>
       </c>
       <c r="N52">
-        <v>345.56408</v>
+        <v>328.5751712</v>
       </c>
       <c r="O52">
-        <v>86.183681552</v>
+        <v>81.94664769728</v>
       </c>
       <c r="P52">
-        <v>259.380398448</v>
+        <v>246.62852350272</v>
       </c>
       <c r="Q52">
-        <v>515.480398448</v>
+        <v>502.72852350272</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.0973650206085336</v>
+        <v>0.09826744483786523</v>
       </c>
       <c r="T52">
-        <v>1.190878074100083</v>
+        <v>1.211719280320213</v>
       </c>
       <c r="U52">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V52">
         <v>0.2494</v>
       </c>
       <c r="W52">
-        <v>0.05396814</v>
+        <v>0.05689548</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.532190881168729</v>
+        <v>2.354810444875985</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07716774277055397</v>
+        <v>0.07720523523684114</v>
       </c>
       <c r="C53">
-        <v>2491.914998998981</v>
+        <v>2426.137956134779</v>
       </c>
       <c r="D53">
-        <v>5200.750998998981</v>
+        <v>5197.70995613478</v>
       </c>
       <c r="E53">
-        <v>1203.436</v>
+        <v>1266.172</v>
       </c>
       <c r="F53">
-        <v>3199.536</v>
+        <v>3262.272</v>
       </c>
       <c r="G53">
         <v>490.7</v>
@@ -5639,28 +5639,28 @@
         <v>571.1</v>
       </c>
       <c r="M53">
-        <v>242.5248288</v>
+        <v>247.2802176</v>
       </c>
       <c r="N53">
-        <v>328.5751712</v>
+        <v>323.8197824</v>
       </c>
       <c r="O53">
-        <v>81.94664769728</v>
+        <v>80.76065373056001</v>
       </c>
       <c r="P53">
-        <v>246.62852350272</v>
+        <v>243.05912866944</v>
       </c>
       <c r="Q53">
-        <v>502.72852350272</v>
+        <v>499.15912866944</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09826744483786523</v>
+        <v>0.09920747007675236</v>
       </c>
       <c r="T53">
-        <v>1.211719280320213</v>
+        <v>1.233428870132849</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.354810444875985</v>
+        <v>2.30952562862837</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07720523523684114</v>
+        <v>0.07724272770312832</v>
       </c>
       <c r="C54">
-        <v>2426.137956134779</v>
+        <v>2360.364467579293</v>
       </c>
       <c r="D54">
-        <v>5197.70995613478</v>
+        <v>5194.672467579293</v>
       </c>
       <c r="E54">
-        <v>1266.172</v>
+        <v>1328.908</v>
       </c>
       <c r="F54">
-        <v>3262.272</v>
+        <v>3325.008</v>
       </c>
       <c r="G54">
         <v>490.7</v>
@@ -5721,28 +5721,28 @@
         <v>571.1</v>
       </c>
       <c r="M54">
-        <v>247.2802176</v>
+        <v>252.0356064</v>
       </c>
       <c r="N54">
-        <v>323.8197824</v>
+        <v>319.0643936</v>
       </c>
       <c r="O54">
-        <v>80.76065373056001</v>
+        <v>79.57465976384</v>
       </c>
       <c r="P54">
-        <v>243.05912866944</v>
+        <v>239.48973383616</v>
       </c>
       <c r="Q54">
-        <v>499.15912866944</v>
+        <v>495.58973383616</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09920747007675236</v>
+        <v>0.1001874963896347</v>
       </c>
       <c r="T54">
-        <v>1.233428870132849</v>
+        <v>1.256062272277938</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.30952562862837</v>
+        <v>2.26594967337123</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07724272770312832</v>
+        <v>0.07728022016941546</v>
       </c>
       <c r="C55">
-        <v>2360.364467579293</v>
+        <v>2294.594527104856</v>
       </c>
       <c r="D55">
-        <v>5194.672467579293</v>
+        <v>5191.638527104857</v>
       </c>
       <c r="E55">
-        <v>1328.908</v>
+        <v>1391.644</v>
       </c>
       <c r="F55">
-        <v>3325.008</v>
+        <v>3387.744000000001</v>
       </c>
       <c r="G55">
         <v>490.7</v>
@@ -5803,28 +5803,28 @@
         <v>571.1</v>
       </c>
       <c r="M55">
-        <v>252.0356064</v>
+        <v>256.7909952000001</v>
       </c>
       <c r="N55">
-        <v>319.0643936</v>
+        <v>314.3090048</v>
       </c>
       <c r="O55">
-        <v>79.57465976384</v>
+        <v>78.38866579712</v>
       </c>
       <c r="P55">
-        <v>239.48973383616</v>
+        <v>235.92033900288</v>
       </c>
       <c r="Q55">
-        <v>495.58973383616</v>
+        <v>492.02033900288</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1001874963896347</v>
+        <v>0.1012101325422075</v>
       </c>
       <c r="T55">
-        <v>1.256062272277938</v>
+        <v>1.279679735385856</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.26594967337123</v>
+        <v>2.223987642382874</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07728022016941546</v>
+        <v>0.07731771263570264</v>
       </c>
       <c r="C56">
-        <v>2294.594527104856</v>
+        <v>2228.828128498342</v>
       </c>
       <c r="D56">
-        <v>5191.638527104857</v>
+        <v>5188.608128498343</v>
       </c>
       <c r="E56">
-        <v>1391.644</v>
+        <v>1454.38</v>
       </c>
       <c r="F56">
-        <v>3387.744000000001</v>
+        <v>3450.48</v>
       </c>
       <c r="G56">
         <v>490.7</v>
@@ -5885,28 +5885,28 @@
         <v>571.1</v>
       </c>
       <c r="M56">
-        <v>256.7909952000001</v>
+        <v>261.546384</v>
       </c>
       <c r="N56">
-        <v>314.3090048</v>
+        <v>309.553616</v>
       </c>
       <c r="O56">
-        <v>78.38866579712</v>
+        <v>77.20267183039999</v>
       </c>
       <c r="P56">
-        <v>235.92033900288</v>
+        <v>232.3509441696</v>
       </c>
       <c r="Q56">
-        <v>492.02033900288</v>
+        <v>488.4509441696</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1012101325422075</v>
+        <v>0.1022782191904503</v>
       </c>
       <c r="T56">
-        <v>1.279679735385856</v>
+        <v>1.304346863520792</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.223987642382874</v>
+        <v>2.183551503430458</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07731771263570264</v>
+        <v>0.07735520510198982</v>
       </c>
       <c r="C57">
-        <v>2228.828128498342</v>
+        <v>2163.065265561125</v>
       </c>
       <c r="D57">
-        <v>5188.608128498343</v>
+        <v>5185.581265561125</v>
       </c>
       <c r="E57">
-        <v>1454.38</v>
+        <v>1517.116</v>
       </c>
       <c r="F57">
-        <v>3450.48</v>
+        <v>3513.216</v>
       </c>
       <c r="G57">
         <v>490.7</v>
@@ -5967,28 +5967,28 @@
         <v>571.1</v>
       </c>
       <c r="M57">
-        <v>261.546384</v>
+        <v>266.3017728</v>
       </c>
       <c r="N57">
-        <v>309.553616</v>
+        <v>304.7982272</v>
       </c>
       <c r="O57">
-        <v>77.20267183039999</v>
+        <v>76.01667786368</v>
       </c>
       <c r="P57">
-        <v>232.3509441696</v>
+        <v>228.78154933632</v>
       </c>
       <c r="Q57">
-        <v>488.4509441696</v>
+        <v>484.88154933632</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1022782191904503</v>
+        <v>0.103394855231795</v>
       </c>
       <c r="T57">
-        <v>1.304346863520792</v>
+        <v>1.330135224752772</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.183551503430458</v>
+        <v>2.144559512297771</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07735520510198982</v>
+        <v>0.07739269756827696</v>
       </c>
       <c r="C58">
-        <v>2163.065265561125</v>
+        <v>2097.305932109035</v>
       </c>
       <c r="D58">
-        <v>5185.581265561125</v>
+        <v>5182.557932109036</v>
       </c>
       <c r="E58">
-        <v>1517.116</v>
+        <v>1579.852000000001</v>
       </c>
       <c r="F58">
-        <v>3513.216</v>
+        <v>3575.952000000001</v>
       </c>
       <c r="G58">
         <v>490.7</v>
@@ -6049,28 +6049,28 @@
         <v>571.1</v>
       </c>
       <c r="M58">
-        <v>266.3017728</v>
+        <v>271.0571616000001</v>
       </c>
       <c r="N58">
-        <v>304.7982272</v>
+        <v>300.0428383999999</v>
       </c>
       <c r="O58">
-        <v>76.01667786368</v>
+        <v>74.83068389695998</v>
       </c>
       <c r="P58">
-        <v>228.78154933632</v>
+        <v>225.21215450304</v>
       </c>
       <c r="Q58">
-        <v>484.88154933632</v>
+        <v>481.31215450304</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.103394855231795</v>
+        <v>0.1045634278332023</v>
       </c>
       <c r="T58">
-        <v>1.330135224752772</v>
+        <v>1.357123044646704</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.144559512297771</v>
+        <v>2.106935661204828</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07739269756827696</v>
+        <v>0.07743019003456414</v>
       </c>
       <c r="C59">
-        <v>2097.305932109035</v>
+        <v>2031.550121972313</v>
       </c>
       <c r="D59">
-        <v>5182.557932109036</v>
+        <v>5179.538121972314</v>
       </c>
       <c r="E59">
-        <v>1579.852000000001</v>
+        <v>1642.588</v>
       </c>
       <c r="F59">
-        <v>3575.952000000001</v>
+        <v>3638.688000000001</v>
       </c>
       <c r="G59">
         <v>490.7</v>
@@ -6131,28 +6131,28 @@
         <v>571.1</v>
       </c>
       <c r="M59">
-        <v>271.0571616000001</v>
+        <v>275.8125504000001</v>
       </c>
       <c r="N59">
-        <v>300.0428383999999</v>
+        <v>295.2874495999999</v>
       </c>
       <c r="O59">
-        <v>74.83068389695998</v>
+        <v>73.64468993023999</v>
       </c>
       <c r="P59">
-        <v>225.21215450304</v>
+        <v>221.64275966976</v>
       </c>
       <c r="Q59">
-        <v>481.31215450304</v>
+        <v>477.7427596697599</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1045634278332023</v>
+        <v>0.1057876467489623</v>
       </c>
       <c r="T59">
-        <v>1.357123044646704</v>
+        <v>1.385395998821299</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.106935661204828</v>
+        <v>2.070609184287503</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07743019003456414</v>
+        <v>0.07746768250085131</v>
       </c>
       <c r="C60">
-        <v>2031.550121972314</v>
+        <v>1965.797828995574</v>
       </c>
       <c r="D60">
-        <v>5179.538121972314</v>
+        <v>5176.521828995574</v>
       </c>
       <c r="E60">
-        <v>1642.588</v>
+        <v>1705.324</v>
       </c>
       <c r="F60">
-        <v>3638.688</v>
+        <v>3701.424</v>
       </c>
       <c r="G60">
         <v>490.7</v>
@@ -6213,28 +6213,28 @@
         <v>571.1</v>
       </c>
       <c r="M60">
-        <v>275.8125504</v>
+        <v>280.5679392</v>
       </c>
       <c r="N60">
-        <v>295.2874496</v>
+        <v>290.5320608</v>
       </c>
       <c r="O60">
-        <v>73.64468993024001</v>
+        <v>72.45869596352</v>
       </c>
       <c r="P60">
-        <v>221.64275966976</v>
+        <v>218.07336483648</v>
       </c>
       <c r="Q60">
-        <v>477.74275966976</v>
+        <v>474.17336483648</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1057876467489622</v>
+        <v>0.107071583660613</v>
       </c>
       <c r="T60">
-        <v>1.385395998821299</v>
+        <v>1.415048121492216</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.070609184287504</v>
+        <v>2.035514113367376</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07746768250085131</v>
+        <v>0.07750517496713848</v>
       </c>
       <c r="C61">
-        <v>1965.797828995574</v>
+        <v>1900.049047037763</v>
       </c>
       <c r="D61">
-        <v>5176.521828995574</v>
+        <v>5173.509047037763</v>
       </c>
       <c r="E61">
-        <v>1705.324</v>
+        <v>1768.06</v>
       </c>
       <c r="F61">
-        <v>3701.424</v>
+        <v>3764.16</v>
       </c>
       <c r="G61">
         <v>490.7</v>
@@ -6295,28 +6295,28 @@
         <v>571.1</v>
       </c>
       <c r="M61">
-        <v>280.5679392</v>
+        <v>285.323328</v>
       </c>
       <c r="N61">
-        <v>290.5320608</v>
+        <v>285.776672</v>
       </c>
       <c r="O61">
-        <v>72.45869596352</v>
+        <v>71.27270199680001</v>
       </c>
       <c r="P61">
-        <v>218.07336483648</v>
+        <v>214.5039700032</v>
       </c>
       <c r="Q61">
-        <v>474.17336483648</v>
+        <v>470.6039700032001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.107071583660613</v>
+        <v>0.1084197174178462</v>
       </c>
       <c r="T61">
-        <v>1.415048121492216</v>
+        <v>1.446182850296679</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.035514113367376</v>
+        <v>2.001588878144587</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07750517496713848</v>
+        <v>0.08404436463342566</v>
       </c>
       <c r="C62">
-        <v>1900.049047037763</v>
+        <v>1360.545949688134</v>
       </c>
       <c r="D62">
-        <v>5173.509047037763</v>
+        <v>4696.741949688134</v>
       </c>
       <c r="E62">
-        <v>1768.06</v>
+        <v>1830.796</v>
       </c>
       <c r="F62">
-        <v>3764.16</v>
+        <v>3826.896</v>
       </c>
       <c r="G62">
         <v>490.7</v>
@@ -6377,45 +6377,45 @@
         <v>571.1</v>
       </c>
       <c r="M62">
-        <v>285.323328</v>
+        <v>344.42064</v>
       </c>
       <c r="N62">
-        <v>285.776672</v>
+        <v>226.67936</v>
       </c>
       <c r="O62">
-        <v>71.27270199680001</v>
+        <v>56.53383238400001</v>
       </c>
       <c r="P62">
-        <v>214.5039700032</v>
+        <v>170.145527616</v>
       </c>
       <c r="Q62">
-        <v>470.6039700032001</v>
+        <v>426.2455276160001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1084197174178462</v>
+        <v>0.109836986239553</v>
       </c>
       <c r="T62">
-        <v>1.446182850296679</v>
+        <v>1.478914231860345</v>
       </c>
       <c r="U62">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V62">
         <v>0.2494</v>
       </c>
       <c r="W62">
-        <v>0.05689548</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.001588878144587</v>
+        <v>1.658146852058576</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08404436463342566</v>
+        <v>0.08418844229971281</v>
       </c>
       <c r="C63">
-        <v>1360.545949688134</v>
+        <v>1288.292741445697</v>
       </c>
       <c r="D63">
-        <v>4696.741949688134</v>
+        <v>4687.224741445697</v>
       </c>
       <c r="E63">
-        <v>1830.796</v>
+        <v>1893.532</v>
       </c>
       <c r="F63">
-        <v>3826.896</v>
+        <v>3889.632</v>
       </c>
       <c r="G63">
         <v>490.7</v>
@@ -6459,28 +6459,28 @@
         <v>571.1</v>
       </c>
       <c r="M63">
-        <v>344.42064</v>
+        <v>350.06688</v>
       </c>
       <c r="N63">
-        <v>226.67936</v>
+        <v>221.0331200000001</v>
       </c>
       <c r="O63">
-        <v>56.53383238400001</v>
+        <v>55.12566012800001</v>
       </c>
       <c r="P63">
-        <v>170.145527616</v>
+        <v>165.907459872</v>
       </c>
       <c r="Q63">
-        <v>426.2455276160001</v>
+        <v>422.007459872</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.109836986239553</v>
+        <v>0.111328848157139</v>
       </c>
       <c r="T63">
-        <v>1.478914231860345</v>
+        <v>1.513368317716836</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.658146852058576</v>
+        <v>1.631402547993115</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08418844229971281</v>
+        <v>0.084332519966</v>
       </c>
       <c r="C64">
-        <v>1288.292741445697</v>
+        <v>1216.078025453552</v>
       </c>
       <c r="D64">
-        <v>4687.224741445697</v>
+        <v>4677.746025453553</v>
       </c>
       <c r="E64">
-        <v>1893.532</v>
+        <v>1956.268</v>
       </c>
       <c r="F64">
-        <v>3889.632</v>
+        <v>3952.368</v>
       </c>
       <c r="G64">
         <v>490.7</v>
@@ -6541,28 +6541,28 @@
         <v>571.1</v>
       </c>
       <c r="M64">
-        <v>350.06688</v>
+        <v>355.71312</v>
       </c>
       <c r="N64">
-        <v>221.0331200000001</v>
+        <v>215.38688</v>
       </c>
       <c r="O64">
-        <v>55.12566012800001</v>
+        <v>53.71748787200001</v>
       </c>
       <c r="P64">
-        <v>165.907459872</v>
+        <v>161.669392128</v>
       </c>
       <c r="Q64">
-        <v>422.007459872</v>
+        <v>417.769392128</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.111328848157139</v>
+        <v>0.1129013512594594</v>
       </c>
       <c r="T64">
-        <v>1.513368317716836</v>
+        <v>1.549684786592596</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.631402547993115</v>
+        <v>1.605507269453542</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.084332519966</v>
+        <v>0.08447659763228715</v>
       </c>
       <c r="C65">
-        <v>1216.078025453552</v>
+        <v>1143.90156866073</v>
       </c>
       <c r="D65">
-        <v>4677.746025453553</v>
+        <v>4668.30556866073</v>
       </c>
       <c r="E65">
-        <v>1956.268</v>
+        <v>2019.004</v>
       </c>
       <c r="F65">
-        <v>3952.368</v>
+        <v>4015.104</v>
       </c>
       <c r="G65">
         <v>490.7</v>
@@ -6623,28 +6623,28 @@
         <v>571.1</v>
       </c>
       <c r="M65">
-        <v>355.71312</v>
+        <v>361.35936</v>
       </c>
       <c r="N65">
-        <v>215.38688</v>
+        <v>209.74064</v>
       </c>
       <c r="O65">
-        <v>53.71748787200001</v>
+        <v>52.309315616</v>
       </c>
       <c r="P65">
-        <v>161.669392128</v>
+        <v>157.431324384</v>
       </c>
       <c r="Q65">
-        <v>417.769392128</v>
+        <v>413.531324384</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1129013512594594</v>
+        <v>0.1145612156452421</v>
       </c>
       <c r="T65">
-        <v>1.549684786592596</v>
+        <v>1.588018837072566</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.605507269453542</v>
+        <v>1.58042121836833</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08447659763228715</v>
+        <v>0.08462067529857432</v>
       </c>
       <c r="C66">
-        <v>1143.90156866073</v>
+        <v>1071.763139893799</v>
       </c>
       <c r="D66">
-        <v>4668.30556866073</v>
+        <v>4658.9031398938</v>
       </c>
       <c r="E66">
-        <v>2019.004</v>
+        <v>2081.740000000001</v>
       </c>
       <c r="F66">
-        <v>4015.104</v>
+        <v>4077.840000000001</v>
       </c>
       <c r="G66">
         <v>490.7</v>
@@ -6705,28 +6705,28 @@
         <v>571.1</v>
       </c>
       <c r="M66">
-        <v>361.35936</v>
+        <v>367.0056</v>
       </c>
       <c r="N66">
-        <v>209.74064</v>
+        <v>204.0944</v>
       </c>
       <c r="O66">
-        <v>52.309315616</v>
+        <v>50.90114336000001</v>
       </c>
       <c r="P66">
-        <v>157.431324384</v>
+        <v>153.19325664</v>
       </c>
       <c r="Q66">
-        <v>413.531324384</v>
+        <v>409.29325664</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1145612156452421</v>
+        <v>0.1163159294244981</v>
       </c>
       <c r="T66">
-        <v>1.588018837072566</v>
+        <v>1.628543404722819</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.58042121836833</v>
+        <v>1.556107045778048</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08462067529857432</v>
+        <v>0.08476475296486148</v>
       </c>
       <c r="C67">
-        <v>1071.763139893799</v>
+        <v>999.6625098380191</v>
       </c>
       <c r="D67">
-        <v>4658.9031398938</v>
+        <v>4649.538509838019</v>
       </c>
       <c r="E67">
-        <v>2081.740000000001</v>
+        <v>2144.476</v>
       </c>
       <c r="F67">
-        <v>4077.840000000001</v>
+        <v>4140.576</v>
       </c>
       <c r="G67">
         <v>490.7</v>
@@ -6787,28 +6787,28 @@
         <v>571.1</v>
       </c>
       <c r="M67">
-        <v>367.0056</v>
+        <v>372.65184</v>
       </c>
       <c r="N67">
-        <v>204.0944</v>
+        <v>198.44816</v>
       </c>
       <c r="O67">
-        <v>50.90114336000001</v>
+        <v>49.49297110400001</v>
       </c>
       <c r="P67">
-        <v>153.19325664</v>
+        <v>148.955188896</v>
       </c>
       <c r="Q67">
-        <v>409.29325664</v>
+        <v>405.055188896</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1163159294244981</v>
+        <v>0.1181738616613573</v>
       </c>
       <c r="T67">
-        <v>1.628543404722819</v>
+        <v>1.671451770470146</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.556107045778048</v>
+        <v>1.532529666296563</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08476475296486148</v>
+        <v>0.08490883063114865</v>
       </c>
       <c r="C68">
-        <v>999.6625098380191</v>
+        <v>927.5994510186792</v>
       </c>
       <c r="D68">
-        <v>4649.538509838019</v>
+        <v>4640.21145101868</v>
       </c>
       <c r="E68">
-        <v>2144.476</v>
+        <v>2207.212</v>
       </c>
       <c r="F68">
-        <v>4140.576</v>
+        <v>4203.312000000001</v>
       </c>
       <c r="G68">
         <v>490.7</v>
@@ -6869,28 +6869,28 @@
         <v>571.1</v>
       </c>
       <c r="M68">
-        <v>372.65184</v>
+        <v>378.2980800000001</v>
       </c>
       <c r="N68">
-        <v>198.44816</v>
+        <v>192.8019199999999</v>
       </c>
       <c r="O68">
-        <v>49.49297110400001</v>
+        <v>48.08479884799998</v>
       </c>
       <c r="P68">
-        <v>148.955188896</v>
+        <v>144.7171211519999</v>
       </c>
       <c r="Q68">
-        <v>405.055188896</v>
+        <v>400.817121152</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1181738616613573</v>
+        <v>0.1201443958519657</v>
       </c>
       <c r="T68">
-        <v>1.671451770470146</v>
+        <v>1.716960643232463</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.532529666296563</v>
+        <v>1.509656089187658</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08490883063114865</v>
+        <v>0.1166767023130959</v>
       </c>
       <c r="C69">
-        <v>927.5994510186792</v>
+        <v>-558.1388813796007</v>
       </c>
       <c r="D69">
-        <v>4640.21145101868</v>
+        <v>3217.2091186204</v>
       </c>
       <c r="E69">
-        <v>2207.212</v>
+        <v>2269.948</v>
       </c>
       <c r="F69">
-        <v>4203.312000000001</v>
+        <v>4266.048000000001</v>
       </c>
       <c r="G69">
         <v>490.7</v>
@@ -6951,45 +6951,45 @@
         <v>571.1</v>
       </c>
       <c r="M69">
-        <v>378.2980800000001</v>
+        <v>626.2558464000001</v>
       </c>
       <c r="N69">
-        <v>192.8019199999999</v>
+        <v>-55.15584640000009</v>
       </c>
       <c r="O69">
-        <v>48.08479884799998</v>
+        <v>-13.75586809216002</v>
       </c>
       <c r="P69">
-        <v>144.7171211519999</v>
+        <v>-41.39997830784007</v>
       </c>
       <c r="Q69">
-        <v>400.817121152</v>
+        <v>214.70002169216</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1201443958519657</v>
+        <v>0.1236129640634156</v>
       </c>
       <c r="T69">
-        <v>1.716960643232463</v>
+        <v>1.797066144651631</v>
       </c>
       <c r="U69">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2494</v>
+        <v>0.2274347470267385</v>
       </c>
       <c r="W69">
-        <v>0.06755399999999999</v>
+        <v>0.1134125791364748</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.509656089187658</v>
+        <v>0.9119276143814694</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1166767023130959</v>
+        <v>0.1176867023130959</v>
       </c>
       <c r="C70">
-        <v>-558.1388813796007</v>
+        <v>-651.9395380066085</v>
       </c>
       <c r="D70">
-        <v>3217.2091186204</v>
+        <v>3186.144461993392</v>
       </c>
       <c r="E70">
-        <v>2269.948</v>
+        <v>2332.684</v>
       </c>
       <c r="F70">
-        <v>4266.048000000001</v>
+        <v>4328.784000000001</v>
       </c>
       <c r="G70">
         <v>490.7</v>
@@ -7033,37 +7033,37 @@
         <v>571.1</v>
       </c>
       <c r="M70">
-        <v>626.2558464000001</v>
+        <v>635.4654912000001</v>
       </c>
       <c r="N70">
-        <v>-55.15584640000009</v>
+        <v>-64.36549120000006</v>
       </c>
       <c r="O70">
-        <v>-13.75586809216002</v>
+        <v>-16.05275350528002</v>
       </c>
       <c r="P70">
-        <v>-41.39997830784007</v>
+        <v>-48.31273769472005</v>
       </c>
       <c r="Q70">
-        <v>214.70002169216</v>
+        <v>207.78726230528</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1236129640634156</v>
+        <v>0.1261230596783645</v>
       </c>
       <c r="T70">
-        <v>1.797066144651631</v>
+        <v>1.855036020285555</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2274347470267385</v>
+        <v>0.2241385912727278</v>
       </c>
       <c r="W70">
-        <v>0.1134125791364748</v>
+        <v>0.1138964548011636</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9119276143814694</v>
+        <v>0.8987112721440568</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1176867023130959</v>
+        <v>0.1186967023130959</v>
       </c>
       <c r="C71">
-        <v>-651.9395380066085</v>
+        <v>-745.1460249557363</v>
       </c>
       <c r="D71">
-        <v>3186.144461993392</v>
+        <v>3155.673975044264</v>
       </c>
       <c r="E71">
-        <v>2332.684</v>
+        <v>2395.42</v>
       </c>
       <c r="F71">
-        <v>4328.784000000001</v>
+        <v>4391.52</v>
       </c>
       <c r="G71">
         <v>490.7</v>
@@ -7115,37 +7115,37 @@
         <v>571.1</v>
       </c>
       <c r="M71">
-        <v>635.4654912000001</v>
+        <v>644.6751360000002</v>
       </c>
       <c r="N71">
-        <v>-64.36549120000006</v>
+        <v>-73.57513600000016</v>
       </c>
       <c r="O71">
-        <v>-16.05275350528002</v>
+        <v>-18.34963891840004</v>
       </c>
       <c r="P71">
-        <v>-48.31273769472005</v>
+        <v>-55.22549708160012</v>
       </c>
       <c r="Q71">
-        <v>207.78726230528</v>
+        <v>200.8745029183999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1261230596783645</v>
+        <v>0.1288004950009767</v>
       </c>
       <c r="T71">
-        <v>1.855036020285555</v>
+        <v>1.916870554295073</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2241385912727278</v>
+        <v>0.2209366113974031</v>
       </c>
       <c r="W71">
-        <v>0.1138964548011636</v>
+        <v>0.1143665054468612</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8987112721440568</v>
+        <v>0.8858725396848559</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1186967023130959</v>
+        <v>0.1197067023130959</v>
       </c>
       <c r="C72">
-        <v>-745.1460249557363</v>
+        <v>-837.7752276543997</v>
       </c>
       <c r="D72">
-        <v>3155.673975044264</v>
+        <v>3125.780772345601</v>
       </c>
       <c r="E72">
-        <v>2395.42</v>
+        <v>2458.156</v>
       </c>
       <c r="F72">
-        <v>4391.52</v>
+        <v>4454.256</v>
       </c>
       <c r="G72">
         <v>490.7</v>
@@ -7197,37 +7197,37 @@
         <v>571.1</v>
       </c>
       <c r="M72">
-        <v>644.6751360000002</v>
+        <v>653.8847808000002</v>
       </c>
       <c r="N72">
-        <v>-73.57513600000016</v>
+        <v>-82.78478080000014</v>
       </c>
       <c r="O72">
-        <v>-18.34963891840004</v>
+        <v>-20.64652433152003</v>
       </c>
       <c r="P72">
-        <v>-55.22549708160012</v>
+        <v>-62.1382564684801</v>
       </c>
       <c r="Q72">
-        <v>200.8745029183999</v>
+        <v>193.9617435315199</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1288004950009767</v>
+        <v>0.1316625810354931</v>
       </c>
       <c r="T72">
-        <v>1.916870554295073</v>
+        <v>1.982969538925938</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2209366113974031</v>
+        <v>0.2178248281382847</v>
       </c>
       <c r="W72">
-        <v>0.1143665054468612</v>
+        <v>0.1148233152292998</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8858725396848559</v>
+        <v>0.8733954616611256</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1197067023130959</v>
+        <v>0.1207167023130959</v>
       </c>
       <c r="C73">
-        <v>-837.7752276543997</v>
+        <v>-929.8433977219961</v>
       </c>
       <c r="D73">
-        <v>3125.780772345601</v>
+        <v>3096.448602278004</v>
       </c>
       <c r="E73">
-        <v>2458.156</v>
+        <v>2520.892</v>
       </c>
       <c r="F73">
-        <v>4454.256</v>
+        <v>4516.992</v>
       </c>
       <c r="G73">
         <v>490.7</v>
@@ -7279,37 +7279,37 @@
         <v>571.1</v>
       </c>
       <c r="M73">
-        <v>653.8847808000002</v>
+        <v>663.0944256000001</v>
       </c>
       <c r="N73">
-        <v>-82.78478080000014</v>
+        <v>-91.99442560000011</v>
       </c>
       <c r="O73">
-        <v>-20.64652433152003</v>
+        <v>-22.94340974464003</v>
       </c>
       <c r="P73">
-        <v>-62.1382564684801</v>
+        <v>-69.05101585536008</v>
       </c>
       <c r="Q73">
-        <v>193.9617435315199</v>
+        <v>187.0489841446399</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1316625810354931</v>
+        <v>0.1347291017867607</v>
       </c>
       <c r="T73">
-        <v>1.982969538925938</v>
+        <v>2.053789879601864</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2178248281382847</v>
+        <v>0.2147994833030308</v>
       </c>
       <c r="W73">
-        <v>0.1148233152292998</v>
+        <v>0.1152674358511151</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8733954616611256</v>
+        <v>0.8612649691380544</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1207167023130959</v>
+        <v>0.1217267023130959</v>
       </c>
       <c r="C74">
-        <v>-929.8433977219961</v>
+        <v>-1021.366182431554</v>
       </c>
       <c r="D74">
-        <v>3096.448602278004</v>
+        <v>3067.661817568446</v>
       </c>
       <c r="E74">
-        <v>2520.892</v>
+        <v>2583.628</v>
       </c>
       <c r="F74">
-        <v>4516.992</v>
+        <v>4579.728</v>
       </c>
       <c r="G74">
         <v>490.7</v>
@@ -7361,37 +7361,37 @@
         <v>571.1</v>
       </c>
       <c r="M74">
-        <v>663.0944256000001</v>
+        <v>672.3040704000001</v>
       </c>
       <c r="N74">
-        <v>-91.99442560000011</v>
+        <v>-101.2040704000001</v>
       </c>
       <c r="O74">
-        <v>-22.94340974464003</v>
+        <v>-25.24029515776002</v>
       </c>
       <c r="P74">
-        <v>-69.05101585536008</v>
+        <v>-75.96377524224008</v>
       </c>
       <c r="Q74">
-        <v>187.0489841446399</v>
+        <v>180.1362247577599</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1347291017867607</v>
+        <v>0.1380227722233074</v>
       </c>
       <c r="T74">
-        <v>2.053789879601864</v>
+        <v>2.12985617143897</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2147994833030308</v>
+        <v>0.2118570246276468</v>
       </c>
       <c r="W74">
-        <v>0.1152674358511151</v>
+        <v>0.1156993887846615</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8612649691380544</v>
+        <v>0.8494668188758893</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1217267023130959</v>
+        <v>0.1227367023130959</v>
       </c>
       <c r="C75">
-        <v>-1021.366182431554</v>
+        <v>-1112.358652543137</v>
       </c>
       <c r="D75">
-        <v>3067.661817568446</v>
+        <v>3039.405347456863</v>
       </c>
       <c r="E75">
-        <v>2583.628</v>
+        <v>2646.364</v>
       </c>
       <c r="F75">
-        <v>4579.728</v>
+        <v>4642.464</v>
       </c>
       <c r="G75">
         <v>490.7</v>
@@ -7443,37 +7443,37 @@
         <v>571.1</v>
       </c>
       <c r="M75">
-        <v>672.3040704000001</v>
+        <v>681.5137152000001</v>
       </c>
       <c r="N75">
-        <v>-101.2040704000001</v>
+        <v>-110.4137152000001</v>
       </c>
       <c r="O75">
-        <v>-25.24029515776002</v>
+        <v>-27.53718057088002</v>
       </c>
       <c r="P75">
-        <v>-75.96377524224008</v>
+        <v>-82.87653462912004</v>
       </c>
       <c r="Q75">
-        <v>180.1362247577599</v>
+        <v>173.22346537088</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1380227722233074</v>
+        <v>0.1415698019242038</v>
       </c>
       <c r="T75">
-        <v>2.12985617143897</v>
+        <v>2.211773716494315</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2118570246276468</v>
+        <v>0.2089940918624083</v>
       </c>
       <c r="W75">
-        <v>0.1156993887846615</v>
+        <v>0.1161196673145985</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8494668188758893</v>
+        <v>0.8379875375397287</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1227367023130959</v>
+        <v>0.1237467023130959</v>
       </c>
       <c r="C76">
-        <v>-1112.358652543137</v>
+        <v>-1202.835328613035</v>
       </c>
       <c r="D76">
-        <v>3039.405347456863</v>
+        <v>3011.664671386965</v>
       </c>
       <c r="E76">
-        <v>2646.364</v>
+        <v>2709.1</v>
       </c>
       <c r="F76">
-        <v>4642.464</v>
+        <v>4705.200000000001</v>
       </c>
       <c r="G76">
         <v>490.7</v>
@@ -7525,37 +7525,37 @@
         <v>571.1</v>
       </c>
       <c r="M76">
-        <v>681.5137152000001</v>
+        <v>690.7233600000002</v>
       </c>
       <c r="N76">
-        <v>-110.4137152000001</v>
+        <v>-119.6233600000002</v>
       </c>
       <c r="O76">
-        <v>-27.53718057088002</v>
+        <v>-29.83406598400004</v>
       </c>
       <c r="P76">
-        <v>-82.87653462912004</v>
+        <v>-89.78929401600013</v>
       </c>
       <c r="Q76">
-        <v>173.22346537088</v>
+        <v>166.3107059839999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1415698019242038</v>
+        <v>0.145400594001172</v>
       </c>
       <c r="T76">
-        <v>2.211773716494315</v>
+        <v>2.300244665154088</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2089940918624083</v>
+        <v>0.2062075039709095</v>
       </c>
       <c r="W76">
-        <v>0.1161196673145985</v>
+        <v>0.1165287384170705</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8379875375397287</v>
+        <v>0.8268143703725321</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1237467023130959</v>
+        <v>0.1247567023130959</v>
       </c>
       <c r="C77">
-        <v>-1202.835328613035</v>
+        <v>-1292.810205875238</v>
       </c>
       <c r="D77">
-        <v>3011.664671386965</v>
+        <v>2984.425794124762</v>
       </c>
       <c r="E77">
-        <v>2709.1</v>
+        <v>2771.836</v>
       </c>
       <c r="F77">
-        <v>4705.200000000001</v>
+        <v>4767.936000000001</v>
       </c>
       <c r="G77">
         <v>490.7</v>
@@ -7607,37 +7607,37 @@
         <v>571.1</v>
       </c>
       <c r="M77">
-        <v>690.7233600000002</v>
+        <v>699.9330048000002</v>
       </c>
       <c r="N77">
-        <v>-119.6233600000002</v>
+        <v>-128.8330048000001</v>
       </c>
       <c r="O77">
-        <v>-29.83406598400004</v>
+        <v>-32.13095139712004</v>
       </c>
       <c r="P77">
-        <v>-89.78929401600013</v>
+        <v>-96.7020534028801</v>
       </c>
       <c r="Q77">
-        <v>166.3107059839999</v>
+        <v>159.3979465971199</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.145400594001172</v>
+        <v>0.1495506187512208</v>
       </c>
       <c r="T77">
-        <v>2.300244665154088</v>
+        <v>2.396088192868842</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2062075039709095</v>
+        <v>0.2034942473397134</v>
       </c>
       <c r="W77">
-        <v>0.1165287384170705</v>
+        <v>0.1169270444905301</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8268143703725321</v>
+        <v>0.815935233920262</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1247567023130959</v>
+        <v>0.1257667023130959</v>
       </c>
       <c r="C78">
-        <v>-1292.810205875238</v>
+        <v>-1382.296777784784</v>
       </c>
       <c r="D78">
-        <v>2984.425794124762</v>
+        <v>2957.675222215217</v>
       </c>
       <c r="E78">
-        <v>2771.836</v>
+        <v>2834.572</v>
       </c>
       <c r="F78">
-        <v>4767.936000000001</v>
+        <v>4830.672</v>
       </c>
       <c r="G78">
         <v>490.7</v>
@@ -7689,37 +7689,37 @@
         <v>571.1</v>
       </c>
       <c r="M78">
-        <v>699.9330048000002</v>
+        <v>709.1426496000001</v>
       </c>
       <c r="N78">
-        <v>-128.8330048000001</v>
+        <v>-138.0426496000001</v>
       </c>
       <c r="O78">
-        <v>-32.13095139712004</v>
+        <v>-34.42783681024003</v>
       </c>
       <c r="P78">
-        <v>-96.7020534028801</v>
+        <v>-103.6148127897601</v>
       </c>
       <c r="Q78">
-        <v>159.3979465971199</v>
+        <v>152.4851872102399</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1495506187512208</v>
+        <v>0.1540615152186652</v>
       </c>
       <c r="T78">
-        <v>2.396088192868842</v>
+        <v>2.500265940384878</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2034942473397134</v>
+        <v>0.2008514649067301</v>
       </c>
       <c r="W78">
-        <v>0.1169270444905301</v>
+        <v>0.117315004951692</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.815935233920262</v>
+        <v>0.8053386724407782</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1257667023130959</v>
+        <v>0.1701217811897852</v>
       </c>
       <c r="C79">
-        <v>-1382.296777784784</v>
+        <v>-2280.434850007674</v>
       </c>
       <c r="D79">
-        <v>2957.675222215217</v>
+        <v>2122.273149992327</v>
       </c>
       <c r="E79">
-        <v>2834.572</v>
+        <v>2897.308</v>
       </c>
       <c r="F79">
-        <v>4830.672</v>
+        <v>4893.408</v>
       </c>
       <c r="G79">
         <v>490.7</v>
@@ -7771,45 +7771,45 @@
         <v>571.1</v>
       </c>
       <c r="M79">
-        <v>709.1426496000001</v>
+        <v>982.5963264000001</v>
       </c>
       <c r="N79">
-        <v>-138.0426496000001</v>
+        <v>-411.4963264</v>
       </c>
       <c r="O79">
-        <v>-34.42783681024003</v>
+        <v>-102.62718380416</v>
       </c>
       <c r="P79">
-        <v>-103.6148127897601</v>
+        <v>-308.86914259584</v>
       </c>
       <c r="Q79">
-        <v>152.4851872102399</v>
+        <v>-52.76914259583998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1540615152186652</v>
+        <v>0.1645510335317382</v>
       </c>
       <c r="T79">
-        <v>2.500265940384878</v>
+        <v>2.742518095421205</v>
       </c>
       <c r="U79">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.2008514649067301</v>
+        <v>0.1449550910920239</v>
       </c>
       <c r="W79">
-        <v>0.117315004951692</v>
+        <v>0.1716930177087216</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.8053386724407782</v>
+        <v>0.5812152810425977</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1701217811897852</v>
+        <v>0.1716717811897853</v>
       </c>
       <c r="C80">
-        <v>-2280.434850007674</v>
+        <v>-2363.913730120071</v>
       </c>
       <c r="D80">
-        <v>2122.273149992327</v>
+        <v>2101.530269879929</v>
       </c>
       <c r="E80">
-        <v>2897.308</v>
+        <v>2960.044</v>
       </c>
       <c r="F80">
-        <v>4893.408</v>
+        <v>4956.144</v>
       </c>
       <c r="G80">
         <v>490.7</v>
@@ -7853,37 +7853,37 @@
         <v>571.1</v>
       </c>
       <c r="M80">
-        <v>982.5963264000001</v>
+        <v>995.1937152</v>
       </c>
       <c r="N80">
-        <v>-411.4963264</v>
+        <v>-424.0937152</v>
       </c>
       <c r="O80">
-        <v>-102.62718380416</v>
+        <v>-105.76897257088</v>
       </c>
       <c r="P80">
-        <v>-308.86914259584</v>
+        <v>-318.32474262912</v>
       </c>
       <c r="Q80">
-        <v>-52.76914259583998</v>
+        <v>-62.22474262911999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1645510335317382</v>
+        <v>0.1702058446522971</v>
       </c>
       <c r="T80">
-        <v>2.742518095421205</v>
+        <v>2.873114195203167</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1449550910920239</v>
+        <v>0.1431202165212387</v>
       </c>
       <c r="W80">
-        <v>0.1716930177087216</v>
+        <v>0.1720614605225353</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5812152810425977</v>
+        <v>0.5738581255863622</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1716717811897853</v>
+        <v>0.1732217811897853</v>
       </c>
       <c r="C81">
-        <v>-2363.913730120071</v>
+        <v>-2446.991057402894</v>
       </c>
       <c r="D81">
-        <v>2101.530269879929</v>
+        <v>2081.188942597107</v>
       </c>
       <c r="E81">
-        <v>2960.044</v>
+        <v>3022.780000000001</v>
       </c>
       <c r="F81">
-        <v>4956.144</v>
+        <v>5018.880000000001</v>
       </c>
       <c r="G81">
         <v>490.7</v>
@@ -7935,37 +7935,37 @@
         <v>571.1</v>
       </c>
       <c r="M81">
-        <v>995.1937152</v>
+        <v>1007.791104</v>
       </c>
       <c r="N81">
-        <v>-424.0937152</v>
+        <v>-436.6911040000002</v>
       </c>
       <c r="O81">
-        <v>-105.76897257088</v>
+        <v>-108.9107613376001</v>
       </c>
       <c r="P81">
-        <v>-318.32474262912</v>
+        <v>-327.7803426624001</v>
       </c>
       <c r="Q81">
-        <v>-62.22474262911999</v>
+        <v>-71.68034266240011</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1702058446522971</v>
+        <v>0.176426136884912</v>
       </c>
       <c r="T81">
-        <v>2.873114195203167</v>
+        <v>3.016769904963326</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1431202165212387</v>
+        <v>0.1413312138147232</v>
       </c>
       <c r="W81">
-        <v>0.1720614605225353</v>
+        <v>0.1724206922660036</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5738581255863622</v>
+        <v>0.5666848990165325</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1732217811897853</v>
+        <v>0.1747717811897853</v>
       </c>
       <c r="C82">
-        <v>-2446.991057402894</v>
+        <v>-2529.678380317703</v>
       </c>
       <c r="D82">
-        <v>2081.188942597107</v>
+        <v>2061.237619682298</v>
       </c>
       <c r="E82">
-        <v>3022.780000000001</v>
+        <v>3085.516000000001</v>
       </c>
       <c r="F82">
-        <v>5018.880000000001</v>
+        <v>5081.616000000001</v>
       </c>
       <c r="G82">
         <v>490.7</v>
@@ -8017,37 +8017,37 @@
         <v>571.1</v>
       </c>
       <c r="M82">
-        <v>1007.791104</v>
+        <v>1020.3884928</v>
       </c>
       <c r="N82">
-        <v>-436.6911040000002</v>
+        <v>-449.2884928000002</v>
       </c>
       <c r="O82">
-        <v>-108.9107613376001</v>
+        <v>-112.05255010432</v>
       </c>
       <c r="P82">
-        <v>-327.7803426624001</v>
+        <v>-337.2359426956801</v>
       </c>
       <c r="Q82">
-        <v>-71.68034266240011</v>
+        <v>-81.13594269568011</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.176426136884912</v>
+        <v>0.18330119672096</v>
       </c>
       <c r="T82">
-        <v>3.016769904963326</v>
+        <v>3.175547268382448</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1413312138147232</v>
+        <v>0.1395863840145415</v>
       </c>
       <c r="W82">
-        <v>0.1724206922660036</v>
+        <v>0.1727710540898801</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5666848990165325</v>
+        <v>0.5596887891521309</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1747717811897853</v>
+        <v>0.1763217811897853</v>
       </c>
       <c r="C83">
-        <v>-2529.678380317703</v>
+        <v>-2611.986808693595</v>
       </c>
       <c r="D83">
-        <v>2061.237619682298</v>
+        <v>2041.665191306406</v>
       </c>
       <c r="E83">
-        <v>3085.516000000001</v>
+        <v>3148.252</v>
       </c>
       <c r="F83">
-        <v>5081.616000000001</v>
+        <v>5144.352000000001</v>
       </c>
       <c r="G83">
         <v>490.7</v>
@@ -8099,37 +8099,37 @@
         <v>571.1</v>
       </c>
       <c r="M83">
-        <v>1020.3884928</v>
+        <v>1032.9858816</v>
       </c>
       <c r="N83">
-        <v>-449.2884928000002</v>
+        <v>-461.8858816000001</v>
       </c>
       <c r="O83">
-        <v>-112.05255010432</v>
+        <v>-115.19433887104</v>
       </c>
       <c r="P83">
-        <v>-337.2359426956801</v>
+        <v>-346.69154272896</v>
       </c>
       <c r="Q83">
-        <v>-81.13594269568011</v>
+        <v>-90.59154272896001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.18330119672096</v>
+        <v>0.1909401520943467</v>
       </c>
       <c r="T83">
-        <v>3.175547268382448</v>
+        <v>3.351966561070362</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1395863840145415</v>
+        <v>0.1378841110387544</v>
       </c>
       <c r="W83">
-        <v>0.1727710540898801</v>
+        <v>0.1731128705034181</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5596887891521309</v>
+        <v>0.5528633161136904</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1763217811897853</v>
+        <v>0.1778717811897852</v>
       </c>
       <c r="C84">
-        <v>-2611.986808693595</v>
+        <v>-2693.927034356427</v>
       </c>
       <c r="D84">
-        <v>2041.665191306406</v>
+        <v>2022.460965643574</v>
       </c>
       <c r="E84">
-        <v>3148.252</v>
+        <v>3210.988</v>
       </c>
       <c r="F84">
-        <v>5144.352000000001</v>
+        <v>5207.088000000001</v>
       </c>
       <c r="G84">
         <v>490.7</v>
@@ -8181,37 +8181,37 @@
         <v>571.1</v>
       </c>
       <c r="M84">
-        <v>1032.9858816</v>
+        <v>1045.5832704</v>
       </c>
       <c r="N84">
-        <v>-461.8858816000001</v>
+        <v>-474.4832704000002</v>
       </c>
       <c r="O84">
-        <v>-115.19433887104</v>
+        <v>-118.33612763776</v>
       </c>
       <c r="P84">
-        <v>-346.69154272896</v>
+        <v>-356.1471427622401</v>
       </c>
       <c r="Q84">
-        <v>-90.59154272896001</v>
+        <v>-100.0471427622401</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1909401520943467</v>
+        <v>0.1994778080998965</v>
       </c>
       <c r="T84">
-        <v>3.351966561070362</v>
+        <v>3.549141064662736</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1378841110387544</v>
+        <v>0.1362228566888899</v>
       </c>
       <c r="W84">
-        <v>0.1731128705034181</v>
+        <v>0.1734464503768709</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5528633161136904</v>
+        <v>0.5462023123050916</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1778717811897852</v>
+        <v>0.1794217811897853</v>
       </c>
       <c r="C85">
-        <v>-2693.927034356427</v>
+        <v>-2775.509350604647</v>
       </c>
       <c r="D85">
-        <v>2022.460965643574</v>
+        <v>2003.614649395353</v>
       </c>
       <c r="E85">
-        <v>3210.988</v>
+        <v>3273.724</v>
       </c>
       <c r="F85">
-        <v>5207.088000000001</v>
+        <v>5269.824000000001</v>
       </c>
       <c r="G85">
         <v>490.7</v>
@@ -8263,37 +8263,37 @@
         <v>571.1</v>
       </c>
       <c r="M85">
-        <v>1045.5832704</v>
+        <v>1058.1806592</v>
       </c>
       <c r="N85">
-        <v>-474.4832704000002</v>
+        <v>-487.0806592</v>
       </c>
       <c r="O85">
-        <v>-118.33612763776</v>
+        <v>-121.47791640448</v>
       </c>
       <c r="P85">
-        <v>-356.1471427622401</v>
+        <v>-365.60274279552</v>
       </c>
       <c r="Q85">
-        <v>-100.0471427622401</v>
+        <v>-109.50274279552</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1994778080998965</v>
+        <v>0.20908267110614</v>
       </c>
       <c r="T85">
-        <v>3.549141064662736</v>
+        <v>3.770962381204158</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1362228566888899</v>
+        <v>0.1346011560140221</v>
       </c>
       <c r="W85">
-        <v>0.1734464503768709</v>
+        <v>0.1737720878723844</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5462023123050916</v>
+        <v>0.5396999038252692</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1794217811897852</v>
+        <v>0.1809717811897853</v>
       </c>
       <c r="C86">
-        <v>-2775.509350604647</v>
+        <v>-2856.743670606267</v>
       </c>
       <c r="D86">
-        <v>2003.614649395354</v>
+        <v>1985.116329393733</v>
       </c>
       <c r="E86">
-        <v>3273.724</v>
+        <v>3336.46</v>
       </c>
       <c r="F86">
-        <v>5269.824000000001</v>
+        <v>5332.56</v>
       </c>
       <c r="G86">
         <v>490.7</v>
@@ -8345,37 +8345,37 @@
         <v>571.1</v>
       </c>
       <c r="M86">
-        <v>1058.1806592</v>
+        <v>1070.778048</v>
       </c>
       <c r="N86">
-        <v>-487.0806592</v>
+        <v>-499.6780480000001</v>
       </c>
       <c r="O86">
-        <v>-121.47791640448</v>
+        <v>-124.6197051712</v>
       </c>
       <c r="P86">
-        <v>-365.60274279552</v>
+        <v>-375.0583428288001</v>
       </c>
       <c r="Q86">
-        <v>-109.50274279552</v>
+        <v>-118.9583428288</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.20908267110614</v>
+        <v>0.219968182513216</v>
       </c>
       <c r="T86">
-        <v>3.770962381204156</v>
+        <v>4.022359873284433</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1346011560140221</v>
+        <v>0.1330176130020925</v>
       </c>
       <c r="W86">
-        <v>0.1737720878723844</v>
+        <v>0.1740900633091798</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5396999038252692</v>
+        <v>0.5333504931920308</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1809717811897853</v>
+        <v>0.1825217811897852</v>
       </c>
       <c r="C87">
-        <v>-2856.743670606267</v>
+        <v>-2937.639544786055</v>
       </c>
       <c r="D87">
-        <v>1985.116329393733</v>
+        <v>1966.956455213945</v>
       </c>
       <c r="E87">
-        <v>3336.46</v>
+        <v>3399.196</v>
       </c>
       <c r="F87">
-        <v>5332.56</v>
+        <v>5395.296</v>
       </c>
       <c r="G87">
         <v>490.7</v>
@@ -8427,37 +8427,37 @@
         <v>571.1</v>
       </c>
       <c r="M87">
-        <v>1070.778048</v>
+        <v>1083.3754368</v>
       </c>
       <c r="N87">
-        <v>-499.6780480000001</v>
+        <v>-512.2754368</v>
       </c>
       <c r="O87">
-        <v>-124.6197051712</v>
+        <v>-127.76149393792</v>
       </c>
       <c r="P87">
-        <v>-375.0583428288001</v>
+        <v>-384.5139428620799</v>
       </c>
       <c r="Q87">
-        <v>-118.9583428288</v>
+        <v>-128.4139428620799</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.219968182513216</v>
+        <v>0.2324087669784456</v>
       </c>
       <c r="T87">
-        <v>4.022359873284433</v>
+        <v>4.309671292804749</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1330176130020925</v>
+        <v>0.1314708965718356</v>
       </c>
       <c r="W87">
-        <v>0.1740900633091798</v>
+        <v>0.1744006439683754</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5333504931920308</v>
+        <v>0.5271487432711932</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1825217811897852</v>
+        <v>0.1840717811897852</v>
       </c>
       <c r="C88">
-        <v>-2937.639544786055</v>
+        <v>-3018.206177267032</v>
       </c>
       <c r="D88">
-        <v>1966.956455213945</v>
+        <v>1949.125822732968</v>
       </c>
       <c r="E88">
-        <v>3399.196</v>
+        <v>3461.932</v>
       </c>
       <c r="F88">
-        <v>5395.296</v>
+        <v>5458.032</v>
       </c>
       <c r="G88">
         <v>490.7</v>
@@ -8509,37 +8509,37 @@
         <v>571.1</v>
       </c>
       <c r="M88">
-        <v>1083.3754368</v>
+        <v>1095.9728256</v>
       </c>
       <c r="N88">
-        <v>-512.2754368</v>
+        <v>-524.8728256000001</v>
       </c>
       <c r="O88">
-        <v>-127.76149393792</v>
+        <v>-130.90328270464</v>
       </c>
       <c r="P88">
-        <v>-384.5139428620799</v>
+        <v>-393.9695428953601</v>
       </c>
       <c r="Q88">
-        <v>-128.4139428620799</v>
+        <v>-137.86954289536</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2324087669784456</v>
+        <v>0.2467632875152492</v>
       </c>
       <c r="T88">
-        <v>4.309671292804749</v>
+        <v>4.641184469174346</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1314708965718356</v>
+        <v>0.1299597368411248</v>
       </c>
       <c r="W88">
-        <v>0.1744006439683754</v>
+        <v>0.1747040848423021</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5271487432711932</v>
+        <v>0.521089562314053</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1840717811897852</v>
+        <v>0.1856217811897853</v>
       </c>
       <c r="C89">
-        <v>-3018.206177267032</v>
+        <v>-3098.452441425742</v>
       </c>
       <c r="D89">
-        <v>1949.125822732968</v>
+        <v>1931.615558574258</v>
       </c>
       <c r="E89">
-        <v>3461.932</v>
+        <v>3524.668</v>
       </c>
       <c r="F89">
-        <v>5458.032</v>
+        <v>5520.768</v>
       </c>
       <c r="G89">
         <v>490.7</v>
@@ -8591,37 +8591,37 @@
         <v>571.1</v>
       </c>
       <c r="M89">
-        <v>1095.9728256</v>
+        <v>1108.5702144</v>
       </c>
       <c r="N89">
-        <v>-524.8728256000001</v>
+        <v>-537.4702143999999</v>
       </c>
       <c r="O89">
-        <v>-130.90328270464</v>
+        <v>-134.04507147136</v>
       </c>
       <c r="P89">
-        <v>-393.9695428953601</v>
+        <v>-403.42514292864</v>
       </c>
       <c r="Q89">
-        <v>-137.86954289536</v>
+        <v>-147.3251429286399</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2467632875152492</v>
+        <v>0.26351022814152</v>
       </c>
       <c r="T89">
-        <v>4.641184469174346</v>
+        <v>5.027949841605542</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1299597368411248</v>
+        <v>0.1284829216497484</v>
       </c>
       <c r="W89">
-        <v>0.1747040848423021</v>
+        <v>0.1750006293327305</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.521089562314053</v>
+        <v>0.5151680900150297</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1856217811897853</v>
+        <v>0.1871717811897853</v>
       </c>
       <c r="C90">
-        <v>-3098.452441425742</v>
+        <v>-3178.386894616525</v>
       </c>
       <c r="D90">
-        <v>1931.615558574258</v>
+        <v>1914.417105383475</v>
       </c>
       <c r="E90">
-        <v>3524.668</v>
+        <v>3587.404</v>
       </c>
       <c r="F90">
-        <v>5520.768</v>
+        <v>5583.504000000001</v>
       </c>
       <c r="G90">
         <v>490.7</v>
@@ -8673,37 +8673,37 @@
         <v>571.1</v>
       </c>
       <c r="M90">
-        <v>1108.5702144</v>
+        <v>1121.1676032</v>
       </c>
       <c r="N90">
-        <v>-537.4702143999999</v>
+        <v>-550.0676032000002</v>
       </c>
       <c r="O90">
-        <v>-134.04507147136</v>
+        <v>-137.1868602380801</v>
       </c>
       <c r="P90">
-        <v>-403.42514292864</v>
+        <v>-412.8807429619202</v>
       </c>
       <c r="Q90">
-        <v>-147.3251429286399</v>
+        <v>-156.7807429619202</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.26351022814152</v>
+        <v>0.2833020670634763</v>
       </c>
       <c r="T90">
-        <v>5.027949841605542</v>
+        <v>5.48503619084241</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1284829216497484</v>
+        <v>0.1270392933166052</v>
       </c>
       <c r="W90">
-        <v>0.1750006293327305</v>
+        <v>0.1752905099020257</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5151680900150297</v>
+        <v>0.5093796845092428</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1871717811897853</v>
+        <v>0.1887217811897852</v>
       </c>
       <c r="C91">
-        <v>-3178.386894616525</v>
+        <v>-3258.017792116133</v>
       </c>
       <c r="D91">
-        <v>1914.417105383475</v>
+        <v>1897.522207883868</v>
       </c>
       <c r="E91">
-        <v>3587.404</v>
+        <v>3650.14</v>
       </c>
       <c r="F91">
-        <v>5583.504000000001</v>
+        <v>5646.240000000001</v>
       </c>
       <c r="G91">
         <v>490.7</v>
@@ -8755,37 +8755,37 @@
         <v>571.1</v>
       </c>
       <c r="M91">
-        <v>1121.1676032</v>
+        <v>1133.764992</v>
       </c>
       <c r="N91">
-        <v>-550.0676032000002</v>
+        <v>-562.6649920000001</v>
       </c>
       <c r="O91">
-        <v>-137.1868602380801</v>
+        <v>-140.3286490048</v>
       </c>
       <c r="P91">
-        <v>-412.8807429619202</v>
+        <v>-422.3363429952001</v>
       </c>
       <c r="Q91">
-        <v>-156.7807429619202</v>
+        <v>-166.2363429952001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2833020670634763</v>
+        <v>0.307052273769824</v>
       </c>
       <c r="T91">
-        <v>5.48503619084241</v>
+        <v>6.033539809926651</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1270392933166052</v>
+        <v>0.1256277456130873</v>
       </c>
       <c r="W91">
-        <v>0.1752905099020257</v>
+        <v>0.1755739486808921</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5093796845092428</v>
+        <v>0.5037199102369179</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1887217811897852</v>
+        <v>0.2226161153138413</v>
       </c>
       <c r="C92">
-        <v>-3258.017792116133</v>
+        <v>-3627.70388418902</v>
       </c>
       <c r="D92">
-        <v>1897.522207883868</v>
+        <v>1590.572115810981</v>
       </c>
       <c r="E92">
-        <v>3650.14</v>
+        <v>3712.876</v>
       </c>
       <c r="F92">
-        <v>5646.240000000001</v>
+        <v>5708.976000000001</v>
       </c>
       <c r="G92">
         <v>490.7</v>
@@ -8837,45 +8837,45 @@
         <v>571.1</v>
       </c>
       <c r="M92">
-        <v>1133.764992</v>
+        <v>1346.1765408</v>
       </c>
       <c r="N92">
-        <v>-562.6649920000001</v>
+        <v>-775.0765408000001</v>
       </c>
       <c r="O92">
-        <v>-140.3286490048</v>
+        <v>-193.30408927552</v>
       </c>
       <c r="P92">
-        <v>-422.3363429952001</v>
+        <v>-581.7724515244801</v>
       </c>
       <c r="Q92">
-        <v>-166.2363429952001</v>
+        <v>-325.67245152448</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.307052273769824</v>
+        <v>0.3415729055670935</v>
       </c>
       <c r="T92">
-        <v>6.033539809926651</v>
+        <v>6.830783038501005</v>
       </c>
       <c r="U92">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1256277456130873</v>
+        <v>0.1058050973874169</v>
       </c>
       <c r="W92">
-        <v>0.1755739486808921</v>
+        <v>0.2108511580360471</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.5037199102369179</v>
+        <v>0.4242385620987045</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2226161153138413</v>
+        <v>0.2245161153138413</v>
       </c>
       <c r="C93">
-        <v>-3627.70388418902</v>
+        <v>-3704.733442671148</v>
       </c>
       <c r="D93">
-        <v>1590.572115810981</v>
+        <v>1576.278557328852</v>
       </c>
       <c r="E93">
-        <v>3712.876</v>
+        <v>3775.612</v>
       </c>
       <c r="F93">
-        <v>5708.976000000001</v>
+        <v>5771.712</v>
       </c>
       <c r="G93">
         <v>490.7</v>
@@ -8919,37 +8919,37 @@
         <v>571.1</v>
       </c>
       <c r="M93">
-        <v>1346.1765408</v>
+        <v>1360.9696896</v>
       </c>
       <c r="N93">
-        <v>-775.0765408000001</v>
+        <v>-789.8696896000002</v>
       </c>
       <c r="O93">
-        <v>-193.30408927552</v>
+        <v>-196.9935005862401</v>
       </c>
       <c r="P93">
-        <v>-581.7724515244801</v>
+        <v>-592.8761890137602</v>
       </c>
       <c r="Q93">
-        <v>-325.67245152448</v>
+        <v>-336.7761890137601</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3415729055670935</v>
+        <v>0.3785445187629803</v>
       </c>
       <c r="T93">
-        <v>6.830783038501005</v>
+        <v>7.684630918313633</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1058050973874169</v>
+        <v>0.1046550419810319</v>
       </c>
       <c r="W93">
-        <v>0.2108511580360471</v>
+        <v>0.2111223411008727</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4242385620987045</v>
+        <v>0.4196272733802402</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2245161153138413</v>
+        <v>0.2264161153138413</v>
       </c>
       <c r="C94">
-        <v>-3704.733442671148</v>
+        <v>-3781.508393160401</v>
       </c>
       <c r="D94">
-        <v>1576.278557328852</v>
+        <v>1562.239606839599</v>
       </c>
       <c r="E94">
-        <v>3775.612</v>
+        <v>3838.348</v>
       </c>
       <c r="F94">
-        <v>5771.712</v>
+        <v>5834.448</v>
       </c>
       <c r="G94">
         <v>490.7</v>
@@ -9001,37 +9001,37 @@
         <v>571.1</v>
       </c>
       <c r="M94">
-        <v>1360.9696896</v>
+        <v>1375.7628384</v>
       </c>
       <c r="N94">
-        <v>-789.8696896000002</v>
+        <v>-804.6628384000002</v>
       </c>
       <c r="O94">
-        <v>-196.9935005862401</v>
+        <v>-200.6829118969601</v>
       </c>
       <c r="P94">
-        <v>-592.8761890137602</v>
+        <v>-603.9799265030401</v>
       </c>
       <c r="Q94">
-        <v>-336.7761890137601</v>
+        <v>-347.8799265030401</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3785445187629803</v>
+        <v>0.4260794500148347</v>
       </c>
       <c r="T94">
-        <v>7.684630918313633</v>
+        <v>8.782435335215583</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1046550419810319</v>
+        <v>0.1035297189489778</v>
       </c>
       <c r="W94">
-        <v>0.2111223411008727</v>
+        <v>0.211387692271831</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4196272733802402</v>
+        <v>0.415115152161098</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2264161153138413</v>
+        <v>0.2283161153138413</v>
       </c>
       <c r="C95">
-        <v>-3781.508393160401</v>
+        <v>-3858.035478515969</v>
       </c>
       <c r="D95">
-        <v>1562.239606839599</v>
+        <v>1548.448521484032</v>
       </c>
       <c r="E95">
-        <v>3838.348</v>
+        <v>3901.084000000001</v>
       </c>
       <c r="F95">
-        <v>5834.448</v>
+        <v>5897.184000000001</v>
       </c>
       <c r="G95">
         <v>490.7</v>
@@ -9083,37 +9083,37 @@
         <v>571.1</v>
       </c>
       <c r="M95">
-        <v>1375.7628384</v>
+        <v>1390.5559872</v>
       </c>
       <c r="N95">
-        <v>-804.6628384000002</v>
+        <v>-819.4559872000003</v>
       </c>
       <c r="O95">
-        <v>-200.6829118969601</v>
+        <v>-204.3723232076801</v>
       </c>
       <c r="P95">
-        <v>-603.9799265030401</v>
+        <v>-615.0836639923202</v>
       </c>
       <c r="Q95">
-        <v>-347.8799265030401</v>
+        <v>-358.9836639923202</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4260794500148347</v>
+        <v>0.4894593583506405</v>
       </c>
       <c r="T95">
-        <v>8.782435335215583</v>
+        <v>10.24617455775151</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1035297189489778</v>
+        <v>0.1024283389601589</v>
       </c>
       <c r="W95">
-        <v>0.211387692271831</v>
+        <v>0.2116473976731945</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.415115152161098</v>
+        <v>0.4106990335210862</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2283161153138413</v>
+        <v>0.2302161153138413</v>
       </c>
       <c r="C96">
-        <v>-3858.035478515969</v>
+        <v>-3934.321205582987</v>
       </c>
       <c r="D96">
-        <v>1548.448521484032</v>
+        <v>1534.898794417014</v>
       </c>
       <c r="E96">
-        <v>3901.084000000001</v>
+        <v>3963.820000000001</v>
       </c>
       <c r="F96">
-        <v>5897.184000000001</v>
+        <v>5959.920000000001</v>
       </c>
       <c r="G96">
         <v>490.7</v>
@@ -9165,37 +9165,37 @@
         <v>571.1</v>
       </c>
       <c r="M96">
-        <v>1390.5559872</v>
+        <v>1405.349136</v>
       </c>
       <c r="N96">
-        <v>-819.4559872000003</v>
+        <v>-834.2491360000002</v>
       </c>
       <c r="O96">
-        <v>-204.3723232076801</v>
+        <v>-208.0617345184001</v>
       </c>
       <c r="P96">
-        <v>-615.0836639923202</v>
+        <v>-626.1874014816002</v>
       </c>
       <c r="Q96">
-        <v>-358.9836639923202</v>
+        <v>-370.0874014816002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4894593583506405</v>
+        <v>0.5781912300207689</v>
       </c>
       <c r="T96">
-        <v>10.24617455775151</v>
+        <v>12.29540946930182</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1024283389601589</v>
+        <v>0.101350145918473</v>
       </c>
       <c r="W96">
-        <v>0.2116473976731945</v>
+        <v>0.2119016355924241</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4106990335210862</v>
+        <v>0.4063758857998117</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2302161153138413</v>
+        <v>0.2321161153138413</v>
       </c>
       <c r="C97">
-        <v>-3934.321205582987</v>
+        <v>-4010.371855429193</v>
       </c>
       <c r="D97">
-        <v>1534.898794417014</v>
+        <v>1521.584144570808</v>
       </c>
       <c r="E97">
-        <v>3963.820000000001</v>
+        <v>4026.556</v>
       </c>
       <c r="F97">
-        <v>5959.920000000001</v>
+        <v>6022.656000000001</v>
       </c>
       <c r="G97">
         <v>490.7</v>
@@ -9247,37 +9247,37 @@
         <v>571.1</v>
       </c>
       <c r="M97">
-        <v>1405.349136</v>
+        <v>1420.1422848</v>
       </c>
       <c r="N97">
-        <v>-834.2491360000002</v>
+        <v>-849.0422848000002</v>
       </c>
       <c r="O97">
-        <v>-208.0617345184001</v>
+        <v>-211.75114582912</v>
       </c>
       <c r="P97">
-        <v>-626.1874014816002</v>
+        <v>-637.2911389708802</v>
       </c>
       <c r="Q97">
-        <v>-370.0874014816002</v>
+        <v>-381.1911389708802</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5781912300207689</v>
+        <v>0.7112890375259614</v>
       </c>
       <c r="T97">
-        <v>12.29540946930182</v>
+        <v>15.36926183662729</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.101350145918473</v>
+        <v>0.1002944152318223</v>
       </c>
       <c r="W97">
-        <v>0.2119016355924241</v>
+        <v>0.2121505768883363</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4063758857998117</v>
+        <v>0.4021428036560636</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2321161153138413</v>
+        <v>0.2340161153138413</v>
       </c>
       <c r="C98">
-        <v>-4010.371855429193</v>
+        <v>-4086.193493053364</v>
       </c>
       <c r="D98">
-        <v>1521.584144570807</v>
+        <v>1508.498506946635</v>
       </c>
       <c r="E98">
-        <v>4026.556</v>
+        <v>4089.291999999999</v>
       </c>
       <c r="F98">
-        <v>6022.656</v>
+        <v>6085.392</v>
       </c>
       <c r="G98">
         <v>490.7</v>
@@ -9329,37 +9329,37 @@
         <v>571.1</v>
       </c>
       <c r="M98">
-        <v>1420.1422848</v>
+        <v>1434.9354336</v>
       </c>
       <c r="N98">
-        <v>-849.0422847999999</v>
+        <v>-863.8354336000001</v>
       </c>
       <c r="O98">
-        <v>-211.75114582912</v>
+        <v>-215.44055713984</v>
       </c>
       <c r="P98">
-        <v>-637.29113897088</v>
+        <v>-648.39487646016</v>
       </c>
       <c r="Q98">
-        <v>-381.1911389708799</v>
+        <v>-392.29487646016</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7112890375259596</v>
+        <v>0.9331187167012797</v>
       </c>
       <c r="T98">
-        <v>15.36926183662725</v>
+        <v>20.492349115503</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1002944152318223</v>
+        <v>0.09926045218819524</v>
       </c>
       <c r="W98">
-        <v>0.2121505768883363</v>
+        <v>0.2123943853740236</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4021428036560637</v>
+        <v>0.3979970015565165</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2340161153138413</v>
+        <v>0.2359161153138413</v>
       </c>
       <c r="C99">
-        <v>-4086.193493053364</v>
+        <v>-4161.791976597073</v>
       </c>
       <c r="D99">
-        <v>1508.498506946635</v>
+        <v>1495.636023402928</v>
       </c>
       <c r="E99">
-        <v>4089.291999999999</v>
+        <v>4152.028</v>
       </c>
       <c r="F99">
-        <v>6085.392</v>
+        <v>6148.128000000001</v>
       </c>
       <c r="G99">
         <v>490.7</v>
@@ -9411,37 +9411,37 @@
         <v>571.1</v>
       </c>
       <c r="M99">
-        <v>1434.9354336</v>
+        <v>1449.7285824</v>
       </c>
       <c r="N99">
-        <v>-863.8354336000001</v>
+        <v>-878.6285824000003</v>
       </c>
       <c r="O99">
-        <v>-215.44055713984</v>
+        <v>-219.1299684505601</v>
       </c>
       <c r="P99">
-        <v>-648.39487646016</v>
+        <v>-659.4986139494401</v>
       </c>
       <c r="Q99">
-        <v>-392.29487646016</v>
+        <v>-403.3986139494401</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9331187167012797</v>
+        <v>1.376778075051919</v>
       </c>
       <c r="T99">
-        <v>20.492349115503</v>
+        <v>30.73852367325449</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09926045218819524</v>
+        <v>0.09824759043117282</v>
       </c>
       <c r="W99">
-        <v>0.2123943853740236</v>
+        <v>0.2126332181763295</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3979970015565165</v>
+        <v>0.3939358076630827</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2359161153138413</v>
+        <v>0.2378161153138413</v>
       </c>
       <c r="C100">
-        <v>-4161.791976597073</v>
+        <v>-4237.172966089144</v>
       </c>
       <c r="D100">
-        <v>1495.636023402928</v>
+        <v>1482.991033910856</v>
       </c>
       <c r="E100">
-        <v>4152.028</v>
+        <v>4214.764</v>
       </c>
       <c r="F100">
-        <v>6148.128000000001</v>
+        <v>6210.864</v>
       </c>
       <c r="G100">
         <v>490.7</v>
@@ -9493,37 +9493,37 @@
         <v>571.1</v>
       </c>
       <c r="M100">
-        <v>1449.7285824</v>
+        <v>1464.5217312</v>
       </c>
       <c r="N100">
-        <v>-878.6285824000003</v>
+        <v>-893.4217312000002</v>
       </c>
       <c r="O100">
-        <v>-219.1299684505601</v>
+        <v>-222.8193797612801</v>
       </c>
       <c r="P100">
-        <v>-659.4986139494401</v>
+        <v>-670.6023514387201</v>
       </c>
       <c r="Q100">
-        <v>-403.3986139494401</v>
+        <v>-414.5023514387201</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.376778075051919</v>
+        <v>2.707756150103839</v>
       </c>
       <c r="T100">
-        <v>30.73852367325449</v>
+        <v>61.47704734650898</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09824759043117282</v>
+        <v>0.09725519052782765</v>
       </c>
       <c r="W100">
-        <v>0.2126332181763295</v>
+        <v>0.2128672260735383</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3939358076630827</v>
+        <v>0.3899566580907283</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2378161153138413</v>
-      </c>
-      <c r="C101">
-        <v>-4237.172966089144</v>
-      </c>
-      <c r="D101">
-        <v>1482.991033910856</v>
-      </c>
-      <c r="E101">
-        <v>4214.764</v>
-      </c>
-      <c r="F101">
-        <v>6210.864</v>
-      </c>
-      <c r="G101">
-        <v>490.7</v>
-      </c>
-      <c r="H101">
-        <v>4277.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>827.2</v>
-      </c>
-      <c r="K101">
-        <v>256.1</v>
-      </c>
-      <c r="L101">
-        <v>571.1</v>
-      </c>
-      <c r="M101">
-        <v>1464.5217312</v>
-      </c>
-      <c r="N101">
-        <v>-893.4217312000002</v>
-      </c>
-      <c r="O101">
-        <v>-222.8193797612801</v>
-      </c>
-      <c r="P101">
-        <v>-670.6023514387201</v>
-      </c>
-      <c r="Q101">
-        <v>-414.5023514387201</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.707756150103839</v>
-      </c>
-      <c r="T101">
-        <v>61.47704734650898</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09725519052782765</v>
-      </c>
-      <c r="W101">
-        <v>0.2128672260735383</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3899566580907283</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
